--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -2826,7 +2826,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3097,6 +3097,9 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3511,7 +3514,11 @@
       <c r="A4" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="5"/>
@@ -3543,7 +3550,11 @@
       <c r="A5" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
@@ -3607,7 +3618,11 @@
       <c r="A7" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="4"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
@@ -3671,7 +3686,11 @@
       <c r="A9" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="5"/>
@@ -3703,7 +3722,11 @@
       <c r="A10" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="4"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="5"/>
@@ -3755,8 +3778,10 @@
       <c r="A13" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>99</v>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C13" s="37"/>
       <c r="D13" s="26"/>
@@ -3766,8 +3791,10 @@
       <c r="A14" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="37" t="s">
-        <v>99</v>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="26"/>
@@ -3777,8 +3804,10 @@
       <c r="A15" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="37" t="s">
-        <v>99</v>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="26"/>
@@ -3788,8 +3817,10 @@
       <c r="A16" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="37" t="s">
-        <v>99</v>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="26"/>
@@ -3799,8 +3830,10 @@
       <c r="A17" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="37" t="s">
-        <v>99</v>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="28"/>
@@ -3821,8 +3854,10 @@
       <c r="A19" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="37" t="s">
-        <v>99</v>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="26"/>
@@ -3832,8 +3867,10 @@
       <c r="A20" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="37" t="s">
-        <v>99</v>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="26"/>
@@ -3843,8 +3880,10 @@
       <c r="A21" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="37" t="s">
-        <v>99</v>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="26"/>
@@ -3854,8 +3893,10 @@
       <c r="A22" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>99</v>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C22" s="37"/>
       <c r="D22" s="26"/>
@@ -3865,8 +3906,10 @@
       <c r="A23" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="37" t="s">
-        <v>99</v>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="28"/>
@@ -3880,35 +3923,47 @@
       <c r="C24" s="37"/>
       <c r="D24" s="40"/>
       <c r="E24" s="39"/>
-      <c r="J24" s="43" t="s">
-        <v>99</v>
+      <c r="J24" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="37" t="s">
-        <v>99</v>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="40"/>
       <c r="E25" s="39"/>
-      <c r="J25" s="43" t="s">
-        <v>125</v>
+      <c r="J25" s="43" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="37" t="s">
-        <v>99</v>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C26" s="37"/>
       <c r="D26" s="40"/>
       <c r="E26" s="39"/>
-      <c r="J26" s="43"/>
+      <c r="J26" s="43" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="46" t="s">
@@ -3918,16 +3973,20 @@
       <c r="C27" s="37"/>
       <c r="D27" s="40"/>
       <c r="E27" s="39"/>
-      <c r="J27" s="43" t="s">
-        <v>131</v>
+      <c r="J27" s="43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="37" t="s">
-        <v>99</v>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="44"/>
@@ -3937,8 +3996,10 @@
       <c r="A29" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="37" t="s">
-        <v>99</v>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="48"/>
@@ -3948,8 +4009,10 @@
       <c r="A30" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="37" t="s">
-        <v>99</v>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="48"/>
@@ -3959,8 +4022,10 @@
       <c r="A31" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="37" t="s">
-        <v>99</v>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C31" s="37"/>
       <c r="D31" s="48"/>
@@ -3970,19 +4035,27 @@
       <c r="A32" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="37" t="s">
-        <v>99</v>
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C32" s="37"/>
-      <c r="D32" s="48"/>
+      <c r="D32" s="48" t="inlineStr">
+        <is>
+          <t>Thiếu xuất PDF báo giá; đã có XLSX và gửi email có preview.</t>
+        </is>
+      </c>
       <c r="E32" s="49"/>
     </row>
     <row r="33">
       <c r="A33" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="B33" s="37" t="s">
-        <v>99</v>
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C33" s="37"/>
       <c r="D33" s="48"/>
@@ -4001,8 +4074,10 @@
       <c r="A35" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="B35" s="37" t="s">
-        <v>99</v>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="48"/>
@@ -4012,8 +4087,10 @@
       <c r="A36" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="B36" s="37" t="s">
-        <v>99</v>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="48"/>
@@ -4023,8 +4100,10 @@
       <c r="A37" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B37" s="37" t="s">
-        <v>99</v>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="48"/>
@@ -4034,8 +4113,10 @@
       <c r="A38" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="B38" s="37" t="s">
-        <v>99</v>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C38" s="37"/>
       <c r="D38" s="48"/>
@@ -4045,8 +4126,10 @@
       <c r="A39" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="B39" s="37" t="s">
-        <v>99</v>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C39" s="37"/>
       <c r="D39" s="48"/>
@@ -4056,8 +4139,10 @@
       <c r="A40" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="37" t="s">
-        <v>99</v>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C40" s="37"/>
       <c r="D40" s="48"/>
@@ -4067,8 +4152,10 @@
       <c r="A41" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="37" t="s">
-        <v>99</v>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="48"/>
@@ -4087,8 +4174,10 @@
       <c r="A43" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="37" t="s">
-        <v>99</v>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C43" s="37"/>
       <c r="D43" s="44"/>
@@ -4098,8 +4187,10 @@
       <c r="A44" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="B44" s="37" t="s">
-        <v>99</v>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="44"/>
@@ -4109,19 +4200,27 @@
       <c r="A45" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="B45" s="37" t="s">
-        <v>99</v>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C45" s="37"/>
-      <c r="D45" s="44"/>
+      <c r="D45" s="44" t="inlineStr">
+        <is>
+          <t>Đã upload video; thiếu quay video trực tiếp trong ứng dụng.</t>
+        </is>
+      </c>
       <c r="E45" s="39"/>
     </row>
     <row r="46">
       <c r="A46" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="B46" s="37" t="s">
-        <v>99</v>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C46" s="37"/>
       <c r="D46" s="44"/>
@@ -4131,8 +4230,10 @@
       <c r="A47" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="B47" s="37" t="s">
-        <v>99</v>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C47" s="37"/>
       <c r="D47" s="44"/>
@@ -4142,8 +4243,10 @@
       <c r="A48" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="B48" s="37" t="s">
-        <v>99</v>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C48" s="37"/>
       <c r="D48" s="44"/>
@@ -4153,8 +4256,10 @@
       <c r="A49" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="B49" s="37" t="s">
-        <v>99</v>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C49" s="37"/>
       <c r="D49" s="44"/>
@@ -4164,8 +4269,10 @@
       <c r="A50" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="B50" s="37" t="s">
-        <v>99</v>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C50" s="37"/>
       <c r="D50" s="44"/>
@@ -4175,8 +4282,10 @@
       <c r="A51" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="B51" s="37" t="s">
-        <v>99</v>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C51" s="37"/>
       <c r="D51" s="44"/>
@@ -4195,8 +4304,10 @@
       <c r="A53" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="B53" s="37" t="s">
-        <v>99</v>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C53" s="37"/>
       <c r="D53" s="48"/>
@@ -4206,19 +4317,27 @@
       <c r="A54" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="B54" s="37" t="s">
-        <v>99</v>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C54" s="37"/>
-      <c r="D54" s="48"/>
+      <c r="D54" s="48" t="inlineStr">
+        <is>
+          <t>Hợp đồng gắn Opportunity/Báo giá/Dự án; thiếu liên kết Lead trực tiếp.</t>
+        </is>
+      </c>
       <c r="E54" s="49"/>
     </row>
     <row r="55">
       <c r="A55" s="44" t="s">
         <v>264</v>
       </c>
-      <c r="B55" s="37" t="s">
-        <v>99</v>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C55" s="37"/>
       <c r="D55" s="48"/>
@@ -4228,8 +4347,10 @@
       <c r="A56" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="B56" s="37" t="s">
-        <v>99</v>
+      <c r="B56" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C56" s="37"/>
       <c r="D56" s="48"/>
@@ -4239,19 +4360,27 @@
       <c r="A57" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="B57" s="37" t="s">
-        <v>99</v>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C57" s="37"/>
-      <c r="D57" s="48"/>
+      <c r="D57" s="48" t="inlineStr">
+        <is>
+          <t>Có lifecycle hợp đồng; thiếu tiến độ thực hiện từ công việc/nghiệm thu.</t>
+        </is>
+      </c>
       <c r="E57" s="49"/>
     </row>
     <row r="58">
       <c r="A58" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="B58" s="37" t="s">
-        <v>99</v>
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C58" s="37"/>
       <c r="D58" s="48"/>
@@ -4261,8 +4390,10 @@
       <c r="A59" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="B59" s="37" t="s">
-        <v>99</v>
+      <c r="B59" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C59" s="37"/>
       <c r="D59" s="48"/>
@@ -4272,8 +4403,10 @@
       <c r="A60" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="B60" s="37" t="s">
-        <v>99</v>
+      <c r="B60" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C60" s="37"/>
       <c r="D60" s="48"/>
@@ -4283,30 +4416,44 @@
       <c r="A61" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="B61" s="37" t="s">
-        <v>99</v>
+      <c r="B61" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C61" s="37"/>
-      <c r="D61" s="48"/>
+      <c r="D61" s="48" t="inlineStr">
+        <is>
+          <t>Có nhắc mốc thanh toán; thiếu nhắc gia hạn/kết thúc hợp đồng.</t>
+        </is>
+      </c>
       <c r="E61" s="49"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="B62" s="37" t="s">
-        <v>99</v>
+      <c r="B62" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="48"/>
+      <c r="D62" s="48" t="inlineStr">
+        <is>
+          <t>Có lịch sử chăm sóc Khách hàng; thiếu timeline riêng theo Hợp đồng.</t>
+        </is>
+      </c>
       <c r="E62" s="49"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>99</v>
+      <c r="B63" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C63" s="37"/>
       <c r="D63" s="48"/>
@@ -4316,8 +4463,10 @@
       <c r="A64" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="B64" s="37" t="s">
-        <v>99</v>
+      <c r="B64" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="48"/>
@@ -4345,8 +4494,10 @@
       <c r="A67" s="40" t="s">
         <v>309</v>
       </c>
-      <c r="B67" s="37" t="s">
-        <v>99</v>
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C67" s="37"/>
       <c r="D67" s="44"/>
@@ -4356,30 +4507,44 @@
       <c r="A68" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="B68" s="37" t="s">
-        <v>99</v>
+      <c r="B68" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C68" s="37"/>
-      <c r="D68" s="44"/>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>Có lưu file thiết kế; thiếu quản lý/xem mô hình 3D chuyên dụng.</t>
+        </is>
+      </c>
       <c r="E68" s="39"/>
     </row>
     <row r="69">
       <c r="A69" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="B69" s="37" t="s">
-        <v>99</v>
+      <c r="B69" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C69" s="37"/>
-      <c r="D69" s="44"/>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>Có lưu bản vẽ Concept; thiếu quản lý mặt bằng công năng theo cấu trúc riêng.</t>
+        </is>
+      </c>
       <c r="E69" s="39"/>
     </row>
     <row r="70">
       <c r="A70" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="B70" s="37" t="s">
-        <v>99</v>
+      <c r="B70" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C70" s="37"/>
       <c r="D70" s="44"/>
@@ -4389,41 +4554,61 @@
       <c r="A71" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B71" s="37" t="s">
-        <v>99</v>
+      <c r="B71" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C71" s="37"/>
-      <c r="D71" s="44"/>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>Có quyết định/yêu cầu chỉnh sửa; thiếu thread phản hồi theo từng file của khách hàng.</t>
+        </is>
+      </c>
       <c r="E71" s="39"/>
     </row>
     <row r="72">
       <c r="A72" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="B72" s="37" t="s">
-        <v>99</v>
+      <c r="B72" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C72" s="37"/>
-      <c r="D72" s="44"/>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>Có nhiều phương án Concept; thiếu revision/version của cùng một phương án.</t>
+        </is>
+      </c>
       <c r="E72" s="39"/>
     </row>
     <row r="73">
       <c r="A73" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>99</v>
+      <c r="B73" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C73" s="37"/>
-      <c r="D73" s="44"/>
+      <c r="D73" s="44" t="inlineStr">
+        <is>
+          <t>Có gate quyết định khách hàng; thiếu ký/chốt trực tiếp trên portal khách hàng.</t>
+        </is>
+      </c>
       <c r="E73" s="39"/>
     </row>
     <row r="74">
       <c r="A74" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>99</v>
+      <c r="B74" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="44"/>
@@ -4442,8 +4627,10 @@
       <c r="A76" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="B76" s="37" t="s">
-        <v>99</v>
+      <c r="B76" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C76" s="37"/>
       <c r="D76" s="44"/>
@@ -4453,8 +4640,10 @@
       <c r="A77" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="B77" s="37" t="s">
-        <v>99</v>
+      <c r="B77" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C77" s="37"/>
       <c r="D77" s="44"/>
@@ -4464,8 +4653,10 @@
       <c r="A78" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="B78" s="37" t="s">
-        <v>99</v>
+      <c r="B78" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C78" s="37"/>
       <c r="D78" s="44"/>
@@ -4475,8 +4666,10 @@
       <c r="A79" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="B79" s="37" t="s">
-        <v>99</v>
+      <c r="B79" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C79" s="37"/>
       <c r="D79" s="44"/>
@@ -4486,8 +4679,10 @@
       <c r="A80" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="B80" s="37" t="s">
-        <v>99</v>
+      <c r="B80" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C80" s="37"/>
       <c r="D80" s="44"/>
@@ -4497,8 +4692,10 @@
       <c r="A81" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="B81" s="37" t="s">
-        <v>99</v>
+      <c r="B81" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C81" s="37"/>
       <c r="D81" s="44"/>
@@ -4508,8 +4705,10 @@
       <c r="A82" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="B82" s="37" t="s">
-        <v>99</v>
+      <c r="B82" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C82" s="37"/>
       <c r="D82" s="44"/>
@@ -4519,8 +4718,10 @@
       <c r="A83" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="B83" s="37" t="s">
-        <v>99</v>
+      <c r="B83" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C83" s="37"/>
       <c r="D83" s="44"/>
@@ -4539,8 +4740,10 @@
       <c r="A85" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="B85" s="37" t="s">
-        <v>99</v>
+      <c r="B85" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C85" s="37"/>
       <c r="D85" s="44"/>
@@ -4550,8 +4753,10 @@
       <c r="A86" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="B86" s="37" t="s">
-        <v>99</v>
+      <c r="B86" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C86" s="37"/>
       <c r="D86" s="44"/>
@@ -4561,8 +4766,10 @@
       <c r="A87" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="B87" s="37" t="s">
-        <v>99</v>
+      <c r="B87" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C87" s="37"/>
       <c r="D87" s="44"/>
@@ -4572,8 +4779,10 @@
       <c r="A88" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="B88" s="37" t="s">
-        <v>99</v>
+      <c r="B88" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C88" s="37"/>
       <c r="D88" s="44"/>
@@ -4583,19 +4792,27 @@
       <c r="A89" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="B89" s="37" t="s">
-        <v>99</v>
+      <c r="B89" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C89" s="37"/>
-      <c r="D89" s="44"/>
+      <c r="D89" s="44" t="inlineStr">
+        <is>
+          <t>Có hồ sơ Shop Drawing theo bộ môn; thiếu liên kết bản vẽ đến WBS/hạng mục thi công ổn định.</t>
+        </is>
+      </c>
       <c r="E89" s="39"/>
     </row>
     <row r="90">
       <c r="A90" s="40" t="s">
         <v>416</v>
       </c>
-      <c r="B90" s="37" t="s">
-        <v>99</v>
+      <c r="B90" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C90" s="37"/>
       <c r="D90" s="44"/>
@@ -4605,8 +4822,10 @@
       <c r="A91" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="B91" s="37" t="s">
-        <v>99</v>
+      <c r="B91" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C91" s="37"/>
       <c r="D91" s="44"/>
@@ -4616,8 +4835,10 @@
       <c r="A92" s="40" t="s">
         <v>431</v>
       </c>
-      <c r="B92" s="37" t="s">
-        <v>99</v>
+      <c r="B92" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C92" s="37"/>
       <c r="D92" s="44"/>
@@ -4636,8 +4857,10 @@
       <c r="A94" s="40" t="s">
         <v>443</v>
       </c>
-      <c r="B94" s="37" t="s">
-        <v>99</v>
+      <c r="B94" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C94" s="37"/>
       <c r="D94" s="44"/>
@@ -4647,19 +4870,27 @@
       <c r="A95" s="40" t="s">
         <v>455</v>
       </c>
-      <c r="B95" s="37" t="s">
-        <v>99</v>
+      <c r="B95" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C95" s="37"/>
-      <c r="D95" s="44"/>
+      <c r="D95" s="44" t="inlineStr">
+        <is>
+          <t>Có tạo revision và lịch sử; thiếu sửa/xóa revision đã ghi nhận an toàn.</t>
+        </is>
+      </c>
       <c r="E95" s="39"/>
     </row>
     <row r="96">
       <c r="A96" s="40" t="s">
         <v>458</v>
       </c>
-      <c r="B96" s="37" t="s">
-        <v>99</v>
+      <c r="B96" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C96" s="37"/>
       <c r="D96" s="44"/>
@@ -4669,8 +4900,10 @@
       <c r="A97" s="40" t="s">
         <v>462</v>
       </c>
-      <c r="B97" s="37" t="s">
-        <v>99</v>
+      <c r="B97" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C97" s="37"/>
       <c r="D97" s="44"/>
@@ -4680,8 +4913,10 @@
       <c r="A98" s="40" t="s">
         <v>465</v>
       </c>
-      <c r="B98" s="37" t="s">
-        <v>99</v>
+      <c r="B98" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C98" s="37"/>
       <c r="D98" s="44"/>
@@ -4691,8 +4926,10 @@
       <c r="A99" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="B99" s="37" t="s">
-        <v>99</v>
+      <c r="B99" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C99" s="37"/>
       <c r="D99" s="44"/>
@@ -4702,8 +4939,10 @@
       <c r="A100" s="40" t="s">
         <v>472</v>
       </c>
-      <c r="B100" s="37" t="s">
-        <v>99</v>
+      <c r="B100" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C100" s="37"/>
       <c r="D100" s="44"/>
@@ -4722,8 +4961,10 @@
       <c r="A102" s="40" t="s">
         <v>479</v>
       </c>
-      <c r="B102" s="37" t="s">
-        <v>99</v>
+      <c r="B102" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C102" s="37"/>
       <c r="D102" s="44"/>
@@ -4733,19 +4974,27 @@
       <c r="A103" s="40" t="s">
         <v>482</v>
       </c>
-      <c r="B103" s="37" t="s">
-        <v>99</v>
+      <c r="B103" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C103" s="37"/>
-      <c r="D103" s="44"/>
+      <c r="D103" s="44" t="inlineStr">
+        <is>
+          <t>Có phát hành IFC; thiếu đóng dấu điện tử lên từng file bản vẽ.</t>
+        </is>
+      </c>
       <c r="E103" s="39"/>
     </row>
     <row r="104">
       <c r="A104" s="40" t="s">
         <v>485</v>
       </c>
-      <c r="B104" s="37" t="s">
-        <v>99</v>
+      <c r="B104" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C104" s="37"/>
       <c r="D104" s="44"/>
@@ -4755,8 +5004,10 @@
       <c r="A105" s="40" t="s">
         <v>490</v>
       </c>
-      <c r="B105" s="37" t="s">
-        <v>99</v>
+      <c r="B105" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C105" s="37"/>
       <c r="D105" s="44"/>
@@ -4766,8 +5017,10 @@
       <c r="A106" s="40" t="s">
         <v>495</v>
       </c>
-      <c r="B106" s="37" t="s">
-        <v>99</v>
+      <c r="B106" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C106" s="37"/>
       <c r="D106" s="44"/>
@@ -4777,8 +5030,10 @@
       <c r="A107" s="40" t="s">
         <v>501</v>
       </c>
-      <c r="B107" s="37" t="s">
-        <v>99</v>
+      <c r="B107" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C107" s="37"/>
       <c r="D107" s="44"/>
@@ -4788,8 +5043,10 @@
       <c r="A108" s="40" t="s">
         <v>504</v>
       </c>
-      <c r="B108" s="37" t="s">
-        <v>99</v>
+      <c r="B108" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C108" s="37"/>
       <c r="D108" s="44"/>
@@ -4817,8 +5074,10 @@
       <c r="A111" s="40" t="s">
         <v>515</v>
       </c>
-      <c r="B111" s="37" t="s">
-        <v>99</v>
+      <c r="B111" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C111" s="37"/>
       <c r="D111" s="48"/>
@@ -4828,8 +5087,10 @@
       <c r="A112" s="40" t="s">
         <v>516</v>
       </c>
-      <c r="B112" s="37" t="s">
-        <v>99</v>
+      <c r="B112" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C112" s="37"/>
       <c r="D112" s="48"/>
@@ -4839,19 +5100,27 @@
       <c r="A113" s="40" t="s">
         <v>518</v>
       </c>
-      <c r="B113" s="37" t="s">
-        <v>99</v>
+      <c r="B113" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C113" s="37"/>
-      <c r="D113" s="80"/>
+      <c r="D113" s="80" t="inlineStr">
+        <is>
+          <t>Có checklist theo dự án; thiếu template bắt buộc theo loại/quy mô công trình.</t>
+        </is>
+      </c>
       <c r="E113" s="81"/>
     </row>
     <row r="114">
       <c r="A114" s="40" t="s">
         <v>519</v>
       </c>
-      <c r="B114" s="37" t="s">
-        <v>99</v>
+      <c r="B114" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C114" s="37"/>
       <c r="D114" s="80"/>
@@ -4861,8 +5130,10 @@
       <c r="A115" s="40" t="s">
         <v>521</v>
       </c>
-      <c r="B115" s="37" t="s">
-        <v>99</v>
+      <c r="B115" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C115" s="37"/>
       <c r="D115" s="82"/>
@@ -4872,8 +5143,10 @@
       <c r="A116" s="40" t="s">
         <v>523</v>
       </c>
-      <c r="B116" s="37" t="s">
-        <v>99</v>
+      <c r="B116" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C116" s="37"/>
       <c r="D116" s="84"/>
@@ -4883,8 +5156,10 @@
       <c r="A117" s="40" t="s">
         <v>524</v>
       </c>
-      <c r="B117" s="37" t="s">
-        <v>99</v>
+      <c r="B117" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C117" s="37"/>
       <c r="D117" s="84"/>
@@ -4894,8 +5169,10 @@
       <c r="A118" s="40" t="s">
         <v>525</v>
       </c>
-      <c r="B118" s="37" t="s">
-        <v>99</v>
+      <c r="B118" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C118" s="37"/>
       <c r="D118" s="44"/>
@@ -4914,8 +5191,10 @@
       <c r="A120" s="40" t="s">
         <v>527</v>
       </c>
-      <c r="B120" s="37" t="s">
-        <v>99</v>
+      <c r="B120" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C120" s="37"/>
       <c r="D120" s="85"/>
@@ -4925,8 +5204,10 @@
       <c r="A121" s="40" t="s">
         <v>531</v>
       </c>
-      <c r="B121" s="37" t="s">
-        <v>99</v>
+      <c r="B121" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C121" s="37"/>
       <c r="D121" s="85"/>
@@ -4936,8 +5217,10 @@
       <c r="A122" s="40" t="s">
         <v>532</v>
       </c>
-      <c r="B122" s="37" t="s">
-        <v>99</v>
+      <c r="B122" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C122" s="37"/>
       <c r="D122" s="44"/>
@@ -4947,8 +5230,10 @@
       <c r="A123" s="40" t="s">
         <v>535</v>
       </c>
-      <c r="B123" s="37" t="s">
-        <v>99</v>
+      <c r="B123" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C123" s="37"/>
       <c r="D123" s="85"/>
@@ -4958,8 +5243,10 @@
       <c r="A124" s="40" t="s">
         <v>539</v>
       </c>
-      <c r="B124" s="37" t="s">
-        <v>99</v>
+      <c r="B124" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C124" s="37"/>
       <c r="D124" s="85"/>
@@ -4969,8 +5256,10 @@
       <c r="A125" s="40" t="s">
         <v>541</v>
       </c>
-      <c r="B125" s="37" t="s">
-        <v>99</v>
+      <c r="B125" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C125" s="37"/>
       <c r="D125" s="85"/>
@@ -4980,8 +5269,10 @@
       <c r="A126" s="40" t="s">
         <v>544</v>
       </c>
-      <c r="B126" s="37" t="s">
-        <v>99</v>
+      <c r="B126" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C126" s="37"/>
       <c r="D126" s="85"/>
@@ -4991,8 +5282,10 @@
       <c r="A127" s="40" t="s">
         <v>548</v>
       </c>
-      <c r="B127" s="37" t="s">
-        <v>99</v>
+      <c r="B127" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C127" s="37"/>
       <c r="D127" s="85"/>
@@ -5020,30 +5313,44 @@
       <c r="A130" s="40" t="s">
         <v>557</v>
       </c>
-      <c r="B130" s="37" t="s">
-        <v>99</v>
+      <c r="B130" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C130" s="37"/>
-      <c r="D130" s="85"/>
+      <c r="D130" s="85" t="inlineStr">
+        <is>
+          <t>Có task và Gantt; thiếu baseline WBS/Gantt có phiên bản và critical path.</t>
+        </is>
+      </c>
       <c r="E130" s="86"/>
     </row>
     <row r="131">
       <c r="A131" s="40" t="s">
         <v>560</v>
       </c>
-      <c r="B131" s="37" t="s">
-        <v>99</v>
+      <c r="B131" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C131" s="37"/>
-      <c r="D131" s="85"/>
+      <c r="D131" s="85" t="inlineStr">
+        <is>
+          <t>Có task/phụ thuộc; thiếu cấu trúc WBS phân cấp và baseline công bố.</t>
+        </is>
+      </c>
       <c r="E131" s="86"/>
     </row>
     <row r="132">
       <c r="A132" s="40" t="s">
         <v>564</v>
       </c>
-      <c r="B132" s="37" t="s">
-        <v>99</v>
+      <c r="B132" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C132" s="37"/>
       <c r="D132" s="85"/>
@@ -5053,8 +5360,10 @@
       <c r="A133" s="40" t="s">
         <v>568</v>
       </c>
-      <c r="B133" s="37" t="s">
-        <v>99</v>
+      <c r="B133" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C133" s="37"/>
       <c r="D133" s="85"/>
@@ -5064,8 +5373,10 @@
       <c r="A134" s="40" t="s">
         <v>572</v>
       </c>
-      <c r="B134" s="37" t="s">
-        <v>99</v>
+      <c r="B134" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C134" s="37"/>
       <c r="D134" s="85"/>
@@ -5075,8 +5386,10 @@
       <c r="A135" s="40" t="s">
         <v>573</v>
       </c>
-      <c r="B135" s="37" t="s">
-        <v>99</v>
+      <c r="B135" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C135" s="37"/>
       <c r="D135" s="85"/>
@@ -5086,30 +5399,44 @@
       <c r="A136" s="40" t="s">
         <v>574</v>
       </c>
-      <c r="B136" s="37" t="s">
-        <v>99</v>
+      <c r="B136" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C136" s="37"/>
-      <c r="D136" s="85"/>
+      <c r="D136" s="85" t="inlineStr">
+        <is>
+          <t>Có Gantt từ task; thiếu baseline, critical path và S-Curve.</t>
+        </is>
+      </c>
       <c r="E136" s="86"/>
     </row>
     <row r="137">
       <c r="A137" s="40" t="s">
         <v>575</v>
       </c>
-      <c r="B137" s="37" t="s">
-        <v>99</v>
+      <c r="B137" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C137" s="37"/>
-      <c r="D137" s="85"/>
+      <c r="D137" s="85" t="inlineStr">
+        <is>
+          <t>Có công việc quá hạn; thiếu cảnh báo lệch baseline &gt;5% kèm recovery plan.</t>
+        </is>
+      </c>
       <c r="E137" s="86"/>
     </row>
     <row r="138">
       <c r="A138" s="40" t="s">
         <v>576</v>
       </c>
-      <c r="B138" s="37" t="s">
-        <v>99</v>
+      <c r="B138" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C138" s="37"/>
       <c r="D138" s="85"/>
@@ -5128,8 +5455,10 @@
       <c r="A140" s="40" t="s">
         <v>578</v>
       </c>
-      <c r="B140" s="37" t="s">
-        <v>99</v>
+      <c r="B140" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C140" s="37"/>
       <c r="D140" s="85"/>
@@ -5139,8 +5468,10 @@
       <c r="A141" s="40" t="s">
         <v>579</v>
       </c>
-      <c r="B141" s="37" t="s">
-        <v>99</v>
+      <c r="B141" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C141" s="37"/>
       <c r="D141" s="85"/>
@@ -5150,30 +5481,44 @@
       <c r="A142" s="40" t="s">
         <v>580</v>
       </c>
-      <c r="B142" s="37" t="s">
-        <v>99</v>
+      <c r="B142" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C142" s="37"/>
-      <c r="D142" s="44"/>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>Có nhật ký ngày; thiếu upload ảnh hiện trường vào nhật ký.</t>
+        </is>
+      </c>
       <c r="E142" s="39"/>
     </row>
     <row r="143">
       <c r="A143" s="40" t="s">
         <v>581</v>
       </c>
-      <c r="B143" s="37" t="s">
-        <v>99</v>
+      <c r="B143" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C143" s="37"/>
-      <c r="D143" s="97"/>
+      <c r="D143" s="97" t="inlineStr">
+        <is>
+          <t>Có nhật ký ngày; thiếu upload video hiện trường vào nhật ký.</t>
+        </is>
+      </c>
       <c r="E143" s="98"/>
     </row>
     <row r="144">
       <c r="A144" s="40" t="s">
         <v>582</v>
       </c>
-      <c r="B144" s="37" t="s">
-        <v>99</v>
+      <c r="B144" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C144" s="37"/>
       <c r="D144" s="97"/>
@@ -5183,8 +5528,10 @@
       <c r="A145" s="40" t="s">
         <v>583</v>
       </c>
-      <c r="B145" s="37" t="s">
-        <v>99</v>
+      <c r="B145" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C145" s="37"/>
       <c r="D145" s="97"/>
@@ -5194,8 +5541,10 @@
       <c r="A146" s="40" t="s">
         <v>584</v>
       </c>
-      <c r="B146" s="37" t="s">
-        <v>99</v>
+      <c r="B146" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C146" s="37"/>
       <c r="D146" s="85"/>
@@ -5205,8 +5554,10 @@
       <c r="A147" s="40" t="s">
         <v>585</v>
       </c>
-      <c r="B147" s="37" t="s">
-        <v>99</v>
+      <c r="B147" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C147" s="37"/>
       <c r="D147" s="85"/>
@@ -5216,8 +5567,10 @@
       <c r="A148" s="40" t="s">
         <v>586</v>
       </c>
-      <c r="B148" s="37" t="s">
-        <v>99</v>
+      <c r="B148" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C148" s="37"/>
       <c r="D148" s="85"/>
@@ -5227,8 +5580,10 @@
       <c r="A149" s="40" t="s">
         <v>587</v>
       </c>
-      <c r="B149" s="37" t="s">
-        <v>99</v>
+      <c r="B149" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C149" s="37"/>
       <c r="D149" s="85"/>
@@ -5247,8 +5602,10 @@
       <c r="A151" s="40" t="s">
         <v>589</v>
       </c>
-      <c r="B151" s="37" t="s">
-        <v>99</v>
+      <c r="B151" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C151" s="37"/>
       <c r="D151" s="99"/>
@@ -5258,8 +5615,10 @@
       <c r="A152" s="40" t="s">
         <v>590</v>
       </c>
-      <c r="B152" s="37" t="s">
-        <v>99</v>
+      <c r="B152" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C152" s="37"/>
       <c r="D152" s="99"/>
@@ -5269,19 +5628,27 @@
       <c r="A153" s="40" t="s">
         <v>591</v>
       </c>
-      <c r="B153" s="37" t="s">
-        <v>99</v>
+      <c r="B153" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C153" s="37"/>
-      <c r="D153" s="99"/>
+      <c r="D153" s="99" t="inlineStr">
+        <is>
+          <t>Có dữ liệu QA/QC; thiếu checklist nghiệm thu bắt buộc theo template NICON.</t>
+        </is>
+      </c>
       <c r="E153" s="86"/>
     </row>
     <row r="154">
       <c r="A154" s="40" t="s">
         <v>592</v>
       </c>
-      <c r="B154" s="37" t="s">
-        <v>99</v>
+      <c r="B154" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C154" s="37"/>
       <c r="D154" s="99"/>
@@ -5291,8 +5658,10 @@
       <c r="A155" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="B155" s="37" t="s">
-        <v>99</v>
+      <c r="B155" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C155" s="37"/>
       <c r="D155" s="99"/>
@@ -5302,19 +5671,27 @@
       <c r="A156" s="40" t="s">
         <v>594</v>
       </c>
-      <c r="B156" s="37" t="s">
-        <v>99</v>
+      <c r="B156" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C156" s="37"/>
-      <c r="D156" s="99"/>
+      <c r="D156" s="99" t="inlineStr">
+        <is>
+          <t>Có Draft/Submitted/Approved/Rejected; thiếu kết quả Đạt/Không đạt riêng theo hạng mục.</t>
+        </is>
+      </c>
       <c r="E156" s="86"/>
     </row>
     <row r="157">
       <c r="A157" s="40" t="s">
         <v>595</v>
       </c>
-      <c r="B157" s="37" t="s">
-        <v>99</v>
+      <c r="B157" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C157" s="37"/>
       <c r="D157" s="99"/>
@@ -5324,8 +5701,10 @@
       <c r="A158" s="40" t="s">
         <v>596</v>
       </c>
-      <c r="B158" s="37" t="s">
-        <v>99</v>
+      <c r="B158" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C158" s="37"/>
       <c r="D158" s="99"/>
@@ -5335,8 +5714,10 @@
       <c r="A159" s="40" t="s">
         <v>597</v>
       </c>
-      <c r="B159" s="37" t="s">
-        <v>99</v>
+      <c r="B159" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C159" s="37"/>
       <c r="D159" s="99"/>
@@ -5355,41 +5736,61 @@
       <c r="A161" s="40" t="s">
         <v>598</v>
       </c>
-      <c r="B161" s="37" t="s">
-        <v>99</v>
+      <c r="B161" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C161" s="37"/>
-      <c r="D161" s="100"/>
+      <c r="D161" s="100" t="inlineStr">
+        <is>
+          <t>Có hồ sơ bàn giao; thiếu gate bàn giao đầy đủ theo hồ sơ ba bên.</t>
+        </is>
+      </c>
       <c r="E161" s="98"/>
     </row>
     <row r="162">
       <c r="A162" s="40" t="s">
         <v>599</v>
       </c>
-      <c r="B162" s="37" t="s">
-        <v>99</v>
+      <c r="B162" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C162" s="37"/>
-      <c r="D162" s="99"/>
+      <c r="D162" s="99" t="inlineStr">
+        <is>
+          <t>Có checklist thủ công; thiếu template tổng thể theo loại công trình đã duyệt.</t>
+        </is>
+      </c>
       <c r="E162" s="86"/>
     </row>
     <row r="163">
       <c r="A163" s="40" t="s">
         <v>600</v>
       </c>
-      <c r="B163" s="37" t="s">
-        <v>99</v>
+      <c r="B163" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C163" s="37"/>
-      <c r="D163" s="99"/>
+      <c r="D163" s="99" t="inlineStr">
+        <is>
+          <t>Có cờ hoàn tất/ghi chú commissioning; thiếu quy trình bước, bằng chứng và xác nhận.</t>
+        </is>
+      </c>
       <c r="E163" s="39"/>
     </row>
     <row r="164">
       <c r="A164" s="40" t="s">
         <v>601</v>
       </c>
-      <c r="B164" s="37" t="s">
-        <v>99</v>
+      <c r="B164" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C164" s="37"/>
       <c r="D164" s="99"/>
@@ -5399,19 +5800,27 @@
       <c r="A165" s="40" t="s">
         <v>602</v>
       </c>
-      <c r="B165" s="37" t="s">
-        <v>99</v>
+      <c r="B165" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C165" s="37"/>
-      <c r="D165" s="99"/>
+      <c r="D165" s="99" t="inlineStr">
+        <is>
+          <t>Có lưu bằng chứng ký; thiếu chữ ký số/xác thực chữ ký từng bên.</t>
+        </is>
+      </c>
       <c r="E165" s="39"/>
     </row>
     <row r="166">
       <c r="A166" s="40" t="s">
         <v>603</v>
       </c>
-      <c r="B166" s="37" t="s">
-        <v>99</v>
+      <c r="B166" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C166" s="37"/>
       <c r="D166" s="99"/>
@@ -5421,8 +5830,10 @@
       <c r="A167" s="40" t="s">
         <v>604</v>
       </c>
-      <c r="B167" s="37" t="s">
-        <v>99</v>
+      <c r="B167" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C167" s="37"/>
       <c r="D167" s="99"/>
@@ -5432,8 +5843,10 @@
       <c r="A168" s="40" t="s">
         <v>605</v>
       </c>
-      <c r="B168" s="37" t="s">
-        <v>99</v>
+      <c r="B168" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C168" s="37"/>
       <c r="D168" s="99"/>
@@ -5452,8 +5865,10 @@
       <c r="A170" s="40" t="s">
         <v>607</v>
       </c>
-      <c r="B170" s="37" t="s">
-        <v>99</v>
+      <c r="B170" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C170" s="37"/>
       <c r="D170" s="44"/>
@@ -5463,19 +5878,27 @@
       <c r="A171" s="40" t="s">
         <v>608</v>
       </c>
-      <c r="B171" s="37" t="s">
-        <v>99</v>
+      <c r="B171" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C171" s="37"/>
-      <c r="D171" s="44"/>
+      <c r="D171" s="44" t="inlineStr">
+        <is>
+          <t>Có liên kết hồ sơ nguồn; thiếu tự tổng hợp đủ biên bản nghiệm thu.</t>
+        </is>
+      </c>
       <c r="E171" s="39"/>
     </row>
     <row r="172">
       <c r="A172" s="40" t="s">
         <v>609</v>
       </c>
-      <c r="B172" s="37" t="s">
-        <v>99</v>
+      <c r="B172" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C172" s="37"/>
       <c r="D172" s="44"/>
@@ -5485,8 +5908,10 @@
       <c r="A173" s="40" t="s">
         <v>610</v>
       </c>
-      <c r="B173" s="37" t="s">
-        <v>99</v>
+      <c r="B173" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C173" s="37"/>
       <c r="D173" s="44"/>
@@ -5496,19 +5921,27 @@
       <c r="A174" s="40" t="s">
         <v>611</v>
       </c>
-      <c r="B174" s="37" t="s">
-        <v>99</v>
+      <c r="B174" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C174" s="37"/>
-      <c r="D174" s="30"/>
+      <c r="D174" s="30" t="inlineStr">
+        <is>
+          <t>Có xuất CSV danh mục; thiếu xuất trọn bộ tệp hồ sơ hoàn công.</t>
+        </is>
+      </c>
       <c r="E174" s="101"/>
     </row>
     <row r="175">
       <c r="A175" s="40" t="s">
         <v>612</v>
       </c>
-      <c r="B175" s="37" t="s">
-        <v>99</v>
+      <c r="B175" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C175" s="37"/>
       <c r="D175" s="30"/>
@@ -5518,8 +5951,10 @@
       <c r="A176" s="40" t="s">
         <v>613</v>
       </c>
-      <c r="B176" s="37" t="s">
-        <v>99</v>
+      <c r="B176" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C176" s="37"/>
       <c r="D176" s="30"/>
@@ -5538,8 +5973,10 @@
       <c r="A178" s="40" t="s">
         <v>615</v>
       </c>
-      <c r="B178" s="37" t="s">
-        <v>99</v>
+      <c r="B178" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C178" s="37"/>
       <c r="D178" s="30"/>
@@ -5549,8 +5986,10 @@
       <c r="A179" s="40" t="s">
         <v>616</v>
       </c>
-      <c r="B179" s="37" t="s">
-        <v>99</v>
+      <c r="B179" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C179" s="37"/>
       <c r="D179" s="30"/>
@@ -5560,19 +5999,27 @@
       <c r="A180" s="40" t="s">
         <v>617</v>
       </c>
-      <c r="B180" s="37" t="s">
-        <v>99</v>
+      <c r="B180" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C180" s="37"/>
-      <c r="D180" s="30"/>
+      <c r="D180" s="30" t="inlineStr">
+        <is>
+          <t>Có mô tả/vị trí lỗi; thiếu attachment ảnh/video chuyên dụng.</t>
+        </is>
+      </c>
       <c r="E180" s="101"/>
     </row>
     <row r="181">
       <c r="A181" s="40" t="s">
         <v>618</v>
       </c>
-      <c r="B181" s="37" t="s">
-        <v>99</v>
+      <c r="B181" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C181" s="37"/>
       <c r="D181" s="30"/>
@@ -5582,8 +6029,10 @@
       <c r="A182" s="40" t="s">
         <v>619</v>
       </c>
-      <c r="B182" s="37" t="s">
-        <v>99</v>
+      <c r="B182" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C182" s="37"/>
       <c r="D182" s="30"/>
@@ -5593,8 +6042,10 @@
       <c r="A183" s="40" t="s">
         <v>620</v>
       </c>
-      <c r="B183" s="37" t="s">
-        <v>99</v>
+      <c r="B183" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C183" s="37"/>
       <c r="D183" s="30"/>
@@ -5604,8 +6055,10 @@
       <c r="A184" s="40" t="s">
         <v>621</v>
       </c>
-      <c r="B184" s="37" t="s">
-        <v>99</v>
+      <c r="B184" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C184" s="37"/>
       <c r="D184" s="30"/>
@@ -5615,8 +6068,10 @@
       <c r="A185" s="40" t="s">
         <v>622</v>
       </c>
-      <c r="B185" s="37" t="s">
-        <v>99</v>
+      <c r="B185" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C185" s="37"/>
       <c r="D185" s="30"/>
@@ -5626,8 +6081,10 @@
       <c r="A186" s="40" t="s">
         <v>623</v>
       </c>
-      <c r="B186" s="37" t="s">
-        <v>99</v>
+      <c r="B186" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C186" s="37"/>
       <c r="D186" s="30"/>
@@ -5655,8 +6112,10 @@
       <c r="A189" s="40" t="s">
         <v>626</v>
       </c>
-      <c r="B189" s="37" t="s">
-        <v>99</v>
+      <c r="B189" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C189" s="37"/>
       <c r="D189" s="30"/>
@@ -5666,8 +6125,10 @@
       <c r="A190" s="40" t="s">
         <v>627</v>
       </c>
-      <c r="B190" s="37" t="s">
-        <v>99</v>
+      <c r="B190" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C190" s="37"/>
       <c r="D190" s="30"/>
@@ -5677,8 +6138,10 @@
       <c r="A191" s="40" t="s">
         <v>628</v>
       </c>
-      <c r="B191" s="37" t="s">
-        <v>99</v>
+      <c r="B191" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C191" s="37"/>
       <c r="D191" s="30"/>
@@ -5688,8 +6151,10 @@
       <c r="A192" s="40" t="s">
         <v>629</v>
       </c>
-      <c r="B192" s="37" t="s">
-        <v>99</v>
+      <c r="B192" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C192" s="37"/>
       <c r="D192" s="30"/>
@@ -5699,19 +6164,27 @@
       <c r="A193" s="40" t="s">
         <v>630</v>
       </c>
-      <c r="B193" s="37" t="s">
-        <v>99</v>
+      <c r="B193" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C193" s="37"/>
-      <c r="D193" s="30"/>
+      <c r="D193" s="30" t="inlineStr">
+        <is>
+          <t>Có liên kết Vendor qua Hợp đồng/Dự án; thiếu danh sách lọc theo Dự án riêng.</t>
+        </is>
+      </c>
       <c r="E193" s="101"/>
     </row>
     <row r="194">
       <c r="A194" s="40" t="s">
         <v>631</v>
       </c>
-      <c r="B194" s="37" t="s">
-        <v>99</v>
+      <c r="B194" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C194" s="37"/>
       <c r="D194" s="30"/>
@@ -5721,8 +6194,10 @@
       <c r="A195" s="40" t="s">
         <v>632</v>
       </c>
-      <c r="B195" s="37" t="s">
-        <v>99</v>
+      <c r="B195" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C195" s="37"/>
       <c r="D195" s="30"/>
@@ -5741,19 +6216,27 @@
       <c r="A197" s="40" t="s">
         <v>634</v>
       </c>
-      <c r="B197" s="37" t="s">
-        <v>99</v>
+      <c r="B197" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C197" s="37"/>
-      <c r="D197" s="30"/>
+      <c r="D197" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa RFQ và ma trận; thiếu thao tác xóa RFQ/bảng so sánh.</t>
+        </is>
+      </c>
       <c r="E197" s="101"/>
     </row>
     <row r="198">
       <c r="A198" s="40" t="s">
         <v>635</v>
       </c>
-      <c r="B198" s="37" t="s">
-        <v>99</v>
+      <c r="B198" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C198" s="37"/>
       <c r="D198" s="30"/>
@@ -5763,8 +6246,10 @@
       <c r="A199" s="40" t="s">
         <v>636</v>
       </c>
-      <c r="B199" s="37" t="s">
-        <v>99</v>
+      <c r="B199" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C199" s="37"/>
       <c r="D199" s="30"/>
@@ -5774,8 +6259,10 @@
       <c r="A200" s="40" t="s">
         <v>637</v>
       </c>
-      <c r="B200" s="37" t="s">
-        <v>99</v>
+      <c r="B200" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C200" s="37"/>
       <c r="D200" s="30"/>
@@ -5785,8 +6272,10 @@
       <c r="A201" s="40" t="s">
         <v>638</v>
       </c>
-      <c r="B201" s="37" t="s">
-        <v>99</v>
+      <c r="B201" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C201" s="37"/>
       <c r="D201" s="30"/>
@@ -5796,8 +6285,10 @@
       <c r="A202" s="40" t="s">
         <v>639</v>
       </c>
-      <c r="B202" s="37" t="s">
-        <v>99</v>
+      <c r="B202" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C202" s="37"/>
       <c r="D202" s="30"/>
@@ -5807,8 +6298,10 @@
       <c r="A203" s="40" t="s">
         <v>640</v>
       </c>
-      <c r="B203" s="37" t="s">
-        <v>99</v>
+      <c r="B203" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C203" s="37"/>
       <c r="D203" s="30"/>
@@ -5818,8 +6311,10 @@
       <c r="A204" s="40" t="s">
         <v>641</v>
       </c>
-      <c r="B204" s="37" t="s">
-        <v>99</v>
+      <c r="B204" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C204" s="37"/>
       <c r="D204" s="30"/>
@@ -5838,19 +6333,27 @@
       <c r="A206" s="40" t="s">
         <v>643</v>
       </c>
-      <c r="B206" s="37" t="s">
-        <v>99</v>
+      <c r="B206" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C206" s="37"/>
-      <c r="D206" s="30"/>
+      <c r="D206" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa đánh giá đối tác; thiếu xóa bản đánh giá.</t>
+        </is>
+      </c>
       <c r="E206" s="101"/>
     </row>
     <row r="207">
       <c r="A207" s="40" t="s">
         <v>644</v>
       </c>
-      <c r="B207" s="37" t="s">
-        <v>99</v>
+      <c r="B207" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C207" s="37"/>
       <c r="D207" s="30"/>
@@ -5860,8 +6363,10 @@
       <c r="A208" s="40" t="s">
         <v>645</v>
       </c>
-      <c r="B208" s="37" t="s">
-        <v>99</v>
+      <c r="B208" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C208" s="37"/>
       <c r="D208" s="30"/>
@@ -5871,8 +6376,10 @@
       <c r="A209" s="40" t="s">
         <v>646</v>
       </c>
-      <c r="B209" s="37" t="s">
-        <v>99</v>
+      <c r="B209" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C209" s="37"/>
       <c r="D209" s="30"/>
@@ -5882,8 +6389,10 @@
       <c r="A210" s="40" t="s">
         <v>647</v>
       </c>
-      <c r="B210" s="37" t="s">
-        <v>99</v>
+      <c r="B210" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C210" s="37"/>
       <c r="D210" s="30"/>
@@ -5893,8 +6402,10 @@
       <c r="A211" s="40" t="s">
         <v>648</v>
       </c>
-      <c r="B211" s="37" t="s">
-        <v>99</v>
+      <c r="B211" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C211" s="37"/>
       <c r="D211" s="30"/>
@@ -5904,11 +6415,17 @@
       <c r="A212" s="40" t="s">
         <v>649</v>
       </c>
-      <c r="B212" s="37" t="s">
-        <v>99</v>
+      <c r="B212" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C212" s="37"/>
-      <c r="D212" s="30"/>
+      <c r="D212" s="30" t="inlineStr">
+        <is>
+          <t>Có danh sách đánh giá theo Dự án; thiếu lọc theo đối tác.</t>
+        </is>
+      </c>
       <c r="E212" s="101"/>
     </row>
     <row r="213">
@@ -5924,19 +6441,27 @@
       <c r="A214" s="40" t="s">
         <v>651</v>
       </c>
-      <c r="B214" s="37" t="s">
-        <v>99</v>
+      <c r="B214" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C214" s="37"/>
-      <c r="D214" s="30"/>
+      <c r="D214" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa BOQ và revision; thiếu thao tác xóa BOQ gốc.</t>
+        </is>
+      </c>
       <c r="E214" s="101"/>
     </row>
     <row r="215">
       <c r="A215" s="40" t="s">
         <v>652</v>
       </c>
-      <c r="B215" s="37" t="s">
-        <v>99</v>
+      <c r="B215" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C215" s="37"/>
       <c r="D215" s="30"/>
@@ -5946,8 +6471,10 @@
       <c r="A216" s="40" t="s">
         <v>653</v>
       </c>
-      <c r="B216" s="37" t="s">
-        <v>99</v>
+      <c r="B216" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C216" s="37"/>
       <c r="D216" s="30"/>
@@ -5957,19 +6484,27 @@
       <c r="A217" s="40" t="s">
         <v>654</v>
       </c>
-      <c r="B217" s="37" t="s">
-        <v>99</v>
+      <c r="B217" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C217" s="37"/>
-      <c r="D217" s="30"/>
+      <c r="D217" s="30" t="inlineStr">
+        <is>
+          <t>Có mã công việc ở BOQ; thiếu ràng buộc với baseline tiến độ thi công.</t>
+        </is>
+      </c>
       <c r="E217" s="101"/>
     </row>
     <row r="218">
       <c r="A218" s="40" t="s">
         <v>655</v>
       </c>
-      <c r="B218" s="37" t="s">
-        <v>99</v>
+      <c r="B218" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C218" s="37"/>
       <c r="D218" s="30"/>
@@ -5979,8 +6514,10 @@
       <c r="A219" s="40" t="s">
         <v>656</v>
       </c>
-      <c r="B219" s="37" t="s">
-        <v>99</v>
+      <c r="B219" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C219" s="37"/>
       <c r="D219" s="30"/>
@@ -5999,19 +6536,27 @@
       <c r="A221" s="40" t="s">
         <v>658</v>
       </c>
-      <c r="B221" s="37" t="s">
-        <v>99</v>
+      <c r="B221" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C221" s="37"/>
-      <c r="D221" s="30"/>
+      <c r="D221" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa MR; thiếu thao tác xóa MR.</t>
+        </is>
+      </c>
       <c r="E221" s="101"/>
     </row>
     <row r="222">
       <c r="A222" s="40" t="s">
         <v>659</v>
       </c>
-      <c r="B222" s="37" t="s">
-        <v>99</v>
+      <c r="B222" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C222" s="37"/>
       <c r="D222" s="30"/>
@@ -6021,8 +6566,10 @@
       <c r="A223" s="40" t="s">
         <v>660</v>
       </c>
-      <c r="B223" s="37" t="s">
-        <v>99</v>
+      <c r="B223" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C223" s="37"/>
       <c r="D223" s="30"/>
@@ -6032,8 +6579,10 @@
       <c r="A224" s="40" t="s">
         <v>661</v>
       </c>
-      <c r="B224" s="37" t="s">
-        <v>99</v>
+      <c r="B224" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C224" s="37"/>
       <c r="D224" s="30"/>
@@ -6043,8 +6592,10 @@
       <c r="A225" s="40" t="s">
         <v>662</v>
       </c>
-      <c r="B225" s="37" t="s">
-        <v>99</v>
+      <c r="B225" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C225" s="37"/>
       <c r="D225" s="30"/>
@@ -6054,8 +6605,10 @@
       <c r="A226" s="40" t="s">
         <v>663</v>
       </c>
-      <c r="B226" s="37" t="s">
-        <v>99</v>
+      <c r="B226" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C226" s="37"/>
       <c r="D226" s="30"/>
@@ -6065,8 +6618,10 @@
       <c r="A227" s="40" t="s">
         <v>664</v>
       </c>
-      <c r="B227" s="37" t="s">
-        <v>99</v>
+      <c r="B227" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C227" s="37"/>
       <c r="D227" s="30"/>
@@ -6085,30 +6640,44 @@
       <c r="A229" s="40" t="s">
         <v>666</v>
       </c>
-      <c r="B229" s="37" t="s">
-        <v>99</v>
+      <c r="B229" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C229" s="37"/>
-      <c r="D229" s="30"/>
+      <c r="D229" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa phiếu nhập và reversal; thiếu xóa phiếu nháp.</t>
+        </is>
+      </c>
       <c r="E229" s="101"/>
     </row>
     <row r="230">
       <c r="A230" s="40" t="s">
         <v>667</v>
       </c>
-      <c r="B230" s="37" t="s">
-        <v>99</v>
+      <c r="B230" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C230" s="37"/>
-      <c r="D230" s="30"/>
+      <c r="D230" s="30" t="inlineStr">
+        <is>
+          <t>Có tạo/sửa phiếu xuất và reversal; thiếu xóa phiếu nháp.</t>
+        </is>
+      </c>
       <c r="E230" s="101"/>
     </row>
     <row r="231">
       <c r="A231" s="40" t="s">
         <v>668</v>
       </c>
-      <c r="B231" s="37" t="s">
-        <v>99</v>
+      <c r="B231" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C231" s="37"/>
       <c r="D231" s="30"/>
@@ -6118,8 +6687,10 @@
       <c r="A232" s="40" t="s">
         <v>669</v>
       </c>
-      <c r="B232" s="37" t="s">
-        <v>99</v>
+      <c r="B232" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C232" s="37"/>
       <c r="D232" s="30"/>
@@ -6129,8 +6700,10 @@
       <c r="A233" s="40" t="s">
         <v>670</v>
       </c>
-      <c r="B233" s="37" t="s">
-        <v>99</v>
+      <c r="B233" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C233" s="37"/>
       <c r="D233" s="30"/>
@@ -6140,19 +6713,27 @@
       <c r="A234" s="40" t="s">
         <v>671</v>
       </c>
-      <c r="B234" s="37" t="s">
-        <v>99</v>
+      <c r="B234" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C234" s="37"/>
-      <c r="D234" s="30"/>
+      <c r="D234" s="30" t="inlineStr">
+        <is>
+          <t>Có phiếu xuất theo công việc; thiếu báo cáo tổng hợp vật tư theo hạng mục.</t>
+        </is>
+      </c>
       <c r="E234" s="101"/>
     </row>
     <row r="235">
       <c r="A235" s="40" t="s">
         <v>672</v>
       </c>
-      <c r="B235" s="37" t="s">
-        <v>99</v>
+      <c r="B235" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C235" s="37"/>
       <c r="D235" s="30"/>
@@ -6171,8 +6752,10 @@
       <c r="A237" s="40" t="s">
         <v>674</v>
       </c>
-      <c r="B237" s="37" t="s">
-        <v>99</v>
+      <c r="B237" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C237" s="37"/>
       <c r="D237" s="30"/>
@@ -6182,8 +6765,10 @@
       <c r="A238" s="40" t="s">
         <v>675</v>
       </c>
-      <c r="B238" s="37" t="s">
-        <v>99</v>
+      <c r="B238" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C238" s="37"/>
       <c r="D238" s="30"/>
@@ -6193,19 +6778,27 @@
       <c r="A239" s="40" t="s">
         <v>676</v>
       </c>
-      <c r="B239" s="37" t="s">
-        <v>99</v>
+      <c r="B239" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C239" s="37"/>
-      <c r="D239" s="30"/>
+      <c r="D239" s="30" t="inlineStr">
+        <is>
+          <t>Có cảnh báo thiếu so với MR; thiếu ngưỡng tồn kho tối thiểu cấu hình.</t>
+        </is>
+      </c>
       <c r="E239" s="101"/>
     </row>
     <row r="240">
       <c r="A240" s="40" t="s">
         <v>677</v>
       </c>
-      <c r="B240" s="37" t="s">
-        <v>99</v>
+      <c r="B240" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C240" s="37"/>
       <c r="D240" s="30"/>
@@ -6215,8 +6808,10 @@
       <c r="A241" s="40" t="s">
         <v>678</v>
       </c>
-      <c r="B241" s="37" t="s">
-        <v>99</v>
+      <c r="B241" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C241" s="37"/>
       <c r="D241" s="30"/>
@@ -6226,8 +6821,10 @@
       <c r="A242" s="40" t="s">
         <v>679</v>
       </c>
-      <c r="B242" s="37" t="s">
-        <v>99</v>
+      <c r="B242" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C242" s="37"/>
       <c r="D242" s="30"/>
@@ -6255,8 +6852,10 @@
       <c r="A245" s="40" t="s">
         <v>682</v>
       </c>
-      <c r="B245" s="37" t="s">
-        <v>99</v>
+      <c r="B245" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C245" s="37"/>
       <c r="D245" s="30"/>
@@ -6266,8 +6865,10 @@
       <c r="A246" s="40" t="s">
         <v>683</v>
       </c>
-      <c r="B246" s="37" t="s">
-        <v>99</v>
+      <c r="B246" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C246" s="37"/>
       <c r="D246" s="30"/>
@@ -6277,8 +6878,10 @@
       <c r="A247" s="40" t="s">
         <v>684</v>
       </c>
-      <c r="B247" s="37" t="s">
-        <v>99</v>
+      <c r="B247" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C247" s="37"/>
       <c r="D247" s="30"/>
@@ -6288,30 +6891,44 @@
       <c r="A248" s="40" t="s">
         <v>685</v>
       </c>
-      <c r="B248" s="37" t="s">
-        <v>99</v>
+      <c r="B248" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C248" s="37"/>
-      <c r="D248" s="30"/>
+      <c r="D248" s="30" t="inlineStr">
+        <is>
+          <t>Có mốc thanh toán; thiếu gate theo nghiệm thu/QS được duyệt.</t>
+        </is>
+      </c>
       <c r="E248" s="101"/>
     </row>
     <row r="249">
       <c r="A249" s="40" t="s">
         <v>686</v>
       </c>
-      <c r="B249" s="37" t="s">
-        <v>99</v>
+      <c r="B249" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C249" s="37"/>
-      <c r="D249" s="30"/>
+      <c r="D249" s="30" t="inlineStr">
+        <is>
+          <t>Có lịch mốc và ngày xác nhận Paid; thiếu sổ thực thu/ứng tiền.</t>
+        </is>
+      </c>
       <c r="E249" s="101"/>
     </row>
     <row r="250">
       <c r="A250" s="40" t="s">
         <v>687</v>
       </c>
-      <c r="B250" s="37" t="s">
-        <v>99</v>
+      <c r="B250" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C250" s="37"/>
       <c r="D250" s="30"/>
@@ -6321,8 +6938,10 @@
       <c r="A251" s="40" t="s">
         <v>688</v>
       </c>
-      <c r="B251" s="37" t="s">
-        <v>99</v>
+      <c r="B251" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C251" s="37"/>
       <c r="D251" s="30"/>
@@ -6332,8 +6951,10 @@
       <c r="A252" s="40" t="s">
         <v>689</v>
       </c>
-      <c r="B252" s="37" t="s">
-        <v>99</v>
+      <c r="B252" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C252" s="37"/>
       <c r="D252" s="30"/>
@@ -6343,8 +6964,10 @@
       <c r="A253" s="40" t="s">
         <v>690</v>
       </c>
-      <c r="B253" s="37" t="s">
-        <v>99</v>
+      <c r="B253" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C253" s="37"/>
       <c r="D253" s="30"/>
@@ -6363,8 +6986,10 @@
       <c r="A255" s="40" t="s">
         <v>692</v>
       </c>
-      <c r="B255" s="37" t="s">
-        <v>99</v>
+      <c r="B255" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C255" s="37"/>
       <c r="D255" s="30"/>
@@ -6374,8 +6999,10 @@
       <c r="A256" s="40" t="s">
         <v>693</v>
       </c>
-      <c r="B256" s="37" t="s">
-        <v>99</v>
+      <c r="B256" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C256" s="37"/>
       <c r="D256" s="30"/>
@@ -6385,8 +7012,10 @@
       <c r="A257" s="40" t="s">
         <v>265</v>
       </c>
-      <c r="B257" s="37" t="s">
-        <v>99</v>
+      <c r="B257" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C257" s="37"/>
       <c r="D257" s="30"/>
@@ -6396,19 +7025,27 @@
       <c r="A258" s="40" t="s">
         <v>694</v>
       </c>
-      <c r="B258" s="37" t="s">
-        <v>99</v>
+      <c r="B258" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C258" s="37"/>
-      <c r="D258" s="30"/>
+      <c r="D258" s="30" t="inlineStr">
+        <is>
+          <t>Có mốc thanh toán Downstream; thiếu liên kết tiến độ/QS đủ điều kiện.</t>
+        </is>
+      </c>
       <c r="E258" s="101"/>
     </row>
     <row r="259">
       <c r="A259" s="40" t="s">
         <v>695</v>
       </c>
-      <c r="B259" s="37" t="s">
-        <v>99</v>
+      <c r="B259" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C259" s="37"/>
       <c r="D259" s="30"/>
@@ -6418,30 +7055,44 @@
       <c r="A260" s="40" t="s">
         <v>696</v>
       </c>
-      <c r="B260" s="37" t="s">
-        <v>99</v>
+      <c r="B260" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C260" s="37"/>
-      <c r="D260" s="30"/>
+      <c r="D260" s="30" t="inlineStr">
+        <is>
+          <t>Có lifecycle hợp đồng; thiếu tiến độ thi công thực tế theo gói thầu.</t>
+        </is>
+      </c>
       <c r="E260" s="101"/>
     </row>
     <row r="261">
       <c r="A261" s="40" t="s">
         <v>697</v>
       </c>
-      <c r="B261" s="37" t="s">
-        <v>99</v>
+      <c r="B261" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C261" s="37"/>
-      <c r="D261" s="30"/>
+      <c r="D261" s="30" t="inlineStr">
+        <is>
+          <t>Có Payment Request/Paid; thiếu lịch sử chi tiền có chứng từ đối soát.</t>
+        </is>
+      </c>
       <c r="E261" s="101"/>
     </row>
     <row r="262">
       <c r="A262" s="40" t="s">
         <v>698</v>
       </c>
-      <c r="B262" s="37" t="s">
-        <v>99</v>
+      <c r="B262" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C262" s="37"/>
       <c r="D262" s="30"/>
@@ -6460,8 +7111,10 @@
       <c r="A264" s="40" t="s">
         <v>700</v>
       </c>
-      <c r="B264" s="37" t="s">
-        <v>99</v>
+      <c r="B264" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C264" s="37"/>
       <c r="D264" s="30"/>
@@ -6471,19 +7124,27 @@
       <c r="A265" s="40" t="s">
         <v>701</v>
       </c>
-      <c r="B265" s="37" t="s">
-        <v>99</v>
+      <c r="B265" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C265" s="37"/>
-      <c r="D265" s="30"/>
+      <c r="D265" s="30" t="inlineStr">
+        <is>
+          <t>Có mô tả VO; thiếu liên kết bản vẽ/revision nguồn bắt buộc.</t>
+        </is>
+      </c>
       <c r="E265" s="101"/>
     </row>
     <row r="266">
       <c r="A266" s="40" t="s">
         <v>702</v>
       </c>
-      <c r="B266" s="37" t="s">
-        <v>99</v>
+      <c r="B266" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C266" s="37"/>
       <c r="D266" s="30"/>
@@ -6493,19 +7154,27 @@
       <c r="A267" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="B267" s="37" t="s">
-        <v>99</v>
+      <c r="B267" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C267" s="37"/>
-      <c r="D267" s="30"/>
+      <c r="D267" s="30" t="inlineStr">
+        <is>
+          <t>VO hiện gắn Hợp đồng Upstream; thiếu VO cho Hợp đồng Downstream.</t>
+        </is>
+      </c>
       <c r="E267" s="101"/>
     </row>
     <row r="268">
       <c r="A268" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="B268" s="37" t="s">
-        <v>99</v>
+      <c r="B268" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C268" s="37"/>
       <c r="D268" s="30"/>
@@ -6515,8 +7184,10 @@
       <c r="A269" s="40" t="s">
         <v>705</v>
       </c>
-      <c r="B269" s="37" t="s">
-        <v>99</v>
+      <c r="B269" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C269" s="37"/>
       <c r="D269" s="30"/>
@@ -6526,8 +7197,10 @@
       <c r="A270" s="40" t="s">
         <v>706</v>
       </c>
-      <c r="B270" s="37" t="s">
-        <v>99</v>
+      <c r="B270" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C270" s="37"/>
       <c r="D270" s="30"/>
@@ -6537,8 +7210,10 @@
       <c r="A271" s="40" t="s">
         <v>707</v>
       </c>
-      <c r="B271" s="37" t="s">
-        <v>99</v>
+      <c r="B271" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C271" s="37"/>
       <c r="D271" s="30"/>
@@ -6557,30 +7232,44 @@
       <c r="A273" s="40" t="s">
         <v>709</v>
       </c>
-      <c r="B273" s="37" t="s">
-        <v>99</v>
+      <c r="B273" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C273" s="37"/>
-      <c r="D273" s="30"/>
+      <c r="D273" s="30" t="inlineStr">
+        <is>
+          <t>Có mốc Upstream Paid/ngày nhận; thiếu chứng từ thu và sổ thực thu.</t>
+        </is>
+      </c>
       <c r="E273" s="101"/>
     </row>
     <row r="274">
       <c r="A274" s="40" t="s">
         <v>710</v>
       </c>
-      <c r="B274" s="37" t="s">
-        <v>99</v>
+      <c r="B274" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C274" s="37"/>
-      <c r="D274" s="30"/>
+      <c r="D274" s="30" t="inlineStr">
+        <is>
+          <t>Có Payment Request Downstream Paid; thiếu sổ chi vật tư/thầu phụ thực tế.</t>
+        </is>
+      </c>
       <c r="E274" s="101"/>
     </row>
     <row r="275">
       <c r="A275" s="40" t="s">
         <v>711</v>
       </c>
-      <c r="B275" s="37" t="s">
-        <v>99</v>
+      <c r="B275" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C275" s="37"/>
       <c r="D275" s="30"/>
@@ -6590,30 +7279,44 @@
       <c r="A276" s="40" t="s">
         <v>712</v>
       </c>
-      <c r="B276" s="37" t="s">
-        <v>99</v>
+      <c r="B276" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C276" s="37"/>
-      <c r="D276" s="30"/>
+      <c r="D276" s="30" t="inlineStr">
+        <is>
+          <t>Có lịch mốc hai chiều; thiếu công nợ từ hóa đơn/chứng từ đã ghi sổ.</t>
+        </is>
+      </c>
       <c r="E276" s="101"/>
     </row>
     <row r="277">
       <c r="A277" s="40" t="s">
         <v>713</v>
       </c>
-      <c r="B277" s="37" t="s">
-        <v>99</v>
+      <c r="B277" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C277" s="37"/>
-      <c r="D277" s="30"/>
+      <c r="D277" s="30" t="inlineStr">
+        <is>
+          <t>Có trạng thái mốc và đề nghị thanh toán; thiếu trạng thái giao dịch thu/chi và đối soát quá hạn.</t>
+        </is>
+      </c>
       <c r="E277" s="101"/>
     </row>
     <row r="278">
       <c r="A278" s="40" t="s">
         <v>714</v>
       </c>
-      <c r="B278" s="37" t="s">
-        <v>99</v>
+      <c r="B278" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C278" s="37"/>
       <c r="D278" s="30"/>
@@ -6623,8 +7326,10 @@
       <c r="A279" s="40" t="s">
         <v>715</v>
       </c>
-      <c r="B279" s="37" t="s">
-        <v>99</v>
+      <c r="B279" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C279" s="37"/>
       <c r="D279" s="30"/>
@@ -6643,8 +7348,10 @@
       <c r="A281" s="40" t="s">
         <v>717</v>
       </c>
-      <c r="B281" s="37" t="s">
-        <v>99</v>
+      <c r="B281" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C281" s="37"/>
       <c r="D281" s="30"/>
@@ -6654,8 +7361,10 @@
       <c r="A282" s="40" t="s">
         <v>718</v>
       </c>
-      <c r="B282" s="37" t="s">
-        <v>99</v>
+      <c r="B282" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C282" s="37"/>
       <c r="D282" s="30"/>
@@ -6665,8 +7374,10 @@
       <c r="A283" s="40" t="s">
         <v>719</v>
       </c>
-      <c r="B283" s="37" t="s">
-        <v>99</v>
+      <c r="B283" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C283" s="37"/>
       <c r="D283" s="30"/>
@@ -6676,8 +7387,10 @@
       <c r="A284" s="40" t="s">
         <v>720</v>
       </c>
-      <c r="B284" s="37" t="s">
-        <v>99</v>
+      <c r="B284" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C284" s="37"/>
       <c r="D284" s="30"/>
@@ -6687,8 +7400,10 @@
       <c r="A285" s="40" t="s">
         <v>721</v>
       </c>
-      <c r="B285" s="37" t="s">
-        <v>99</v>
+      <c r="B285" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C285" s="37"/>
       <c r="D285" s="30"/>
@@ -6698,8 +7413,10 @@
       <c r="A286" s="40" t="s">
         <v>722</v>
       </c>
-      <c r="B286" s="37" t="s">
-        <v>99</v>
+      <c r="B286" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C286" s="37"/>
       <c r="D286" s="30"/>
@@ -6709,8 +7426,10 @@
       <c r="A287" s="40" t="s">
         <v>723</v>
       </c>
-      <c r="B287" s="37" t="s">
-        <v>99</v>
+      <c r="B287" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C287" s="37"/>
       <c r="D287" s="30"/>
@@ -6738,8 +7457,10 @@
       <c r="A290" s="40" t="s">
         <v>726</v>
       </c>
-      <c r="B290" s="37" t="s">
-        <v>99</v>
+      <c r="B290" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C290" s="37"/>
       <c r="D290" s="85"/>
@@ -6749,19 +7470,27 @@
       <c r="A291" s="40" t="s">
         <v>727</v>
       </c>
-      <c r="B291" s="37" t="s">
-        <v>99</v>
+      <c r="B291" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C291" s="37"/>
-      <c r="D291" s="85"/>
+      <c r="D291" s="85" t="inlineStr">
+        <is>
+          <t>Có danh mục thư mục cấu hình; Survey còn tách CRM Pre-Design, chưa migration topology mục tiêu.</t>
+        </is>
+      </c>
       <c r="E291" s="86"/>
     </row>
     <row r="292">
       <c r="A292" s="40" t="s">
         <v>728</v>
       </c>
-      <c r="B292" s="37" t="s">
-        <v>99</v>
+      <c r="B292" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C292" s="37"/>
       <c r="D292" s="44"/>
@@ -6771,8 +7500,10 @@
       <c r="A293" s="40" t="s">
         <v>729</v>
       </c>
-      <c r="B293" s="37" t="s">
-        <v>99</v>
+      <c r="B293" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C293" s="37"/>
       <c r="D293" s="97"/>
@@ -6782,30 +7513,44 @@
       <c r="A294" s="40" t="s">
         <v>730</v>
       </c>
-      <c r="B294" s="37" t="s">
-        <v>99</v>
+      <c r="B294" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C294" s="37"/>
-      <c r="D294" s="97"/>
+      <c r="D294" s="97" t="inlineStr">
+        <is>
+          <t>Có quyền tài liệu qua API; thiếu đồng bộ ACL từng thư mục Google Drive theo vai trò.</t>
+        </is>
+      </c>
       <c r="E294" s="98"/>
     </row>
     <row r="295">
       <c r="A295" s="40" t="s">
         <v>731</v>
       </c>
-      <c r="B295" s="37" t="s">
-        <v>99</v>
+      <c r="B295" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C295" s="37"/>
-      <c r="D295" s="97"/>
+      <c r="D295" s="97" t="inlineStr">
+        <is>
+          <t>Có đổi mã Dự án/rename folder; thiếu chỉnh cấu trúc cây thư mục dự án an toàn.</t>
+        </is>
+      </c>
       <c r="E295" s="98"/>
     </row>
     <row r="296">
       <c r="A296" s="40" t="s">
         <v>732</v>
       </c>
-      <c r="B296" s="37" t="s">
-        <v>99</v>
+      <c r="B296" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C296" s="37"/>
       <c r="D296" s="85"/>
@@ -6815,8 +7560,10 @@
       <c r="A297" s="40" t="s">
         <v>733</v>
       </c>
-      <c r="B297" s="37" t="s">
-        <v>99</v>
+      <c r="B297" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C297" s="37"/>
       <c r="D297" s="85"/>
@@ -6835,8 +7582,10 @@
       <c r="A299" s="40" t="s">
         <v>735</v>
       </c>
-      <c r="B299" s="37" t="s">
-        <v>99</v>
+      <c r="B299" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C299" s="37"/>
       <c r="D299" s="85"/>
@@ -6846,8 +7595,10 @@
       <c r="A300" s="40" t="s">
         <v>736</v>
       </c>
-      <c r="B300" s="37" t="s">
-        <v>99</v>
+      <c r="B300" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C300" s="37"/>
       <c r="D300" s="85"/>
@@ -6857,8 +7608,10 @@
       <c r="A301" s="40" t="s">
         <v>737</v>
       </c>
-      <c r="B301" s="37" t="s">
-        <v>99</v>
+      <c r="B301" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C301" s="37"/>
       <c r="D301" s="44"/>
@@ -6868,8 +7621,10 @@
       <c r="A302" s="40" t="s">
         <v>738</v>
       </c>
-      <c r="B302" s="37" t="s">
-        <v>99</v>
+      <c r="B302" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C302" s="37"/>
       <c r="D302" s="97"/>
@@ -6879,8 +7634,10 @@
       <c r="A303" s="40" t="s">
         <v>739</v>
       </c>
-      <c r="B303" s="37" t="s">
-        <v>99</v>
+      <c r="B303" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C303" s="37"/>
       <c r="D303" s="97"/>
@@ -6890,8 +7647,10 @@
       <c r="A304" s="40" t="s">
         <v>740</v>
       </c>
-      <c r="B304" s="37" t="s">
-        <v>99</v>
+      <c r="B304" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C304" s="37"/>
       <c r="D304" s="97"/>
@@ -6901,8 +7660,10 @@
       <c r="A305" s="40" t="s">
         <v>741</v>
       </c>
-      <c r="B305" s="37" t="s">
-        <v>99</v>
+      <c r="B305" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C305" s="37"/>
       <c r="D305" s="85"/>
@@ -6912,8 +7673,10 @@
       <c r="A306" s="40" t="s">
         <v>742</v>
       </c>
-      <c r="B306" s="37" t="s">
-        <v>99</v>
+      <c r="B306" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C306" s="37"/>
       <c r="D306" s="85"/>
@@ -6923,8 +7686,10 @@
       <c r="A307" s="40" t="s">
         <v>743</v>
       </c>
-      <c r="B307" s="37" t="s">
-        <v>99</v>
+      <c r="B307" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C307" s="37"/>
       <c r="D307" s="40"/>
@@ -6952,30 +7717,44 @@
       <c r="A310" s="40" t="s">
         <v>746</v>
       </c>
-      <c r="B310" s="37" t="s">
-        <v>99</v>
+      <c r="B310" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C310" s="37"/>
-      <c r="D310" s="85"/>
+      <c r="D310" s="85" t="inlineStr">
+        <is>
+          <t>Có tiến độ thiết kế và đếm task thi công; thiếu % thi công theo baseline.</t>
+        </is>
+      </c>
       <c r="E310" s="86"/>
     </row>
     <row r="311">
       <c r="A311" s="40" t="s">
         <v>747</v>
       </c>
-      <c r="B311" s="37" t="s">
-        <v>99</v>
+      <c r="B311" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C311" s="37"/>
-      <c r="D311" s="85"/>
+      <c r="D311" s="85" t="inlineStr">
+        <is>
+          <t>Có kế hoạch/thực tế task; thiếu so sánh với baseline S-Curve đã công bố.</t>
+        </is>
+      </c>
       <c r="E311" s="86"/>
     </row>
     <row r="312">
       <c r="A312" s="40" t="s">
         <v>748</v>
       </c>
-      <c r="B312" s="37" t="s">
-        <v>99</v>
+      <c r="B312" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C312" s="37"/>
       <c r="D312" s="44"/>
@@ -6985,19 +7764,27 @@
       <c r="A313" s="40" t="s">
         <v>749</v>
       </c>
-      <c r="B313" s="37" t="s">
-        <v>99</v>
+      <c r="B313" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C313" s="37"/>
-      <c r="D313" s="97"/>
+      <c r="D313" s="97" t="inlineStr">
+        <is>
+          <t>Có % task thiết kế/thi công; thiếu rollup trọng số WBS thi công.</t>
+        </is>
+      </c>
       <c r="E313" s="98"/>
     </row>
     <row r="314">
       <c r="A314" s="40" t="s">
         <v>750</v>
       </c>
-      <c r="B314" s="37" t="s">
-        <v>99</v>
+      <c r="B314" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C314" s="37"/>
       <c r="D314" s="97"/>
@@ -7007,8 +7794,10 @@
       <c r="A315" s="40" t="s">
         <v>751</v>
       </c>
-      <c r="B315" s="37" t="s">
-        <v>99</v>
+      <c r="B315" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C315" s="37"/>
       <c r="D315" s="97"/>
@@ -7018,8 +7807,10 @@
       <c r="A316" s="40" t="s">
         <v>752</v>
       </c>
-      <c r="B316" s="37" t="s">
-        <v>99</v>
+      <c r="B316" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C316" s="37"/>
       <c r="D316" s="85"/>
@@ -7038,19 +7829,27 @@
       <c r="A318" s="40" t="s">
         <v>754</v>
       </c>
-      <c r="B318" s="37" t="s">
-        <v>99</v>
+      <c r="B318" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C318" s="37"/>
-      <c r="D318" s="85"/>
+      <c r="D318" s="85" t="inlineStr">
+        <is>
+          <t>Có số lượng nghiệm thu; thiếu tỷ lệ đạt/không đạt có mẫu số chuẩn.</t>
+        </is>
+      </c>
       <c r="E318" s="86"/>
     </row>
     <row r="319">
       <c r="A319" s="40" t="s">
         <v>755</v>
       </c>
-      <c r="B319" s="37" t="s">
-        <v>99</v>
+      <c r="B319" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C319" s="37"/>
       <c r="D319" s="85"/>
@@ -7060,8 +7859,10 @@
       <c r="A320" s="40" t="s">
         <v>756</v>
       </c>
-      <c r="B320" s="37" t="s">
-        <v>99</v>
+      <c r="B320" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C320" s="37"/>
       <c r="D320" s="44"/>
@@ -7071,44 +7872,68 @@
       <c r="A321" s="40" t="s">
         <v>757</v>
       </c>
-      <c r="B321" s="37" t="s">
-        <v>99</v>
+      <c r="B321" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C321" s="37"/>
-      <c r="D321" s="97"/>
+      <c r="D321" s="97" t="inlineStr">
+        <is>
+          <t>Có file nghiệm thu theo hồ sơ; thiếu danh mục tổng hợp biên bản theo Dự án.</t>
+        </is>
+      </c>
       <c r="E321" s="98"/>
     </row>
     <row r="322">
       <c r="A322" s="40" t="s">
         <v>758</v>
       </c>
-      <c r="B322" s="37" t="s">
-        <v>99</v>
+      <c r="B322" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C322" s="37"/>
-      <c r="D322" s="97"/>
+      <c r="D322" s="97" t="inlineStr">
+        <is>
+          <t>Có ngày/trạng thái nghiệm thu; thiếu báo cáo tiến độ theo giai đoạn thi công.</t>
+        </is>
+      </c>
       <c r="E322" s="98"/>
     </row>
     <row r="323">
       <c r="A323" s="40" t="s">
         <v>759</v>
       </c>
-      <c r="B323" s="37" t="s">
-        <v>99</v>
+      <c r="B323" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C323" s="37"/>
-      <c r="D323" s="97"/>
+      <c r="D323" s="97" t="inlineStr">
+        <is>
+          <t>Có lọc Dự án; thiếu lọc báo cáo theo hạng mục nghiệm thu.</t>
+        </is>
+      </c>
       <c r="E323" s="98"/>
     </row>
     <row r="324">
       <c r="A324" s="40" t="s">
         <v>760</v>
       </c>
-      <c r="B324" s="37" t="s">
-        <v>99</v>
+      <c r="B324" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C324" s="37"/>
-      <c r="D324" s="85"/>
+      <c r="D324" s="85" t="inlineStr">
+        <is>
+          <t>Có xuất báo cáo Dự án; thiếu báo cáo nghiệm thu chi tiết/chứng từ.</t>
+        </is>
+      </c>
       <c r="E324" s="86"/>
     </row>
     <row r="325">
@@ -7124,8 +7949,10 @@
       <c r="A326" s="40" t="s">
         <v>717</v>
       </c>
-      <c r="B326" s="37" t="s">
-        <v>99</v>
+      <c r="B326" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C326" s="37"/>
       <c r="D326" s="85"/>
@@ -7135,8 +7962,10 @@
       <c r="A327" s="40" t="s">
         <v>762</v>
       </c>
-      <c r="B327" s="37" t="s">
-        <v>99</v>
+      <c r="B327" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C327" s="37"/>
       <c r="D327" s="85"/>
@@ -7146,8 +7975,10 @@
       <c r="A328" s="40" t="s">
         <v>763</v>
       </c>
-      <c r="B328" s="37" t="s">
-        <v>99</v>
+      <c r="B328" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C328" s="37"/>
       <c r="D328" s="44"/>
@@ -7157,8 +7988,10 @@
       <c r="A329" s="40" t="s">
         <v>764</v>
       </c>
-      <c r="B329" s="37" t="s">
-        <v>99</v>
+      <c r="B329" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C329" s="37"/>
       <c r="D329" s="97"/>
@@ -7168,8 +8001,10 @@
       <c r="A330" s="40" t="s">
         <v>765</v>
       </c>
-      <c r="B330" s="37" t="s">
-        <v>99</v>
+      <c r="B330" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C330" s="37"/>
       <c r="D330" s="97"/>
@@ -7179,8 +8014,10 @@
       <c r="A331" s="40" t="s">
         <v>766</v>
       </c>
-      <c r="B331" s="37" t="s">
-        <v>99</v>
+      <c r="B331" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C331" s="37"/>
       <c r="D331" s="97"/>
@@ -7190,8 +8027,10 @@
       <c r="A332" s="40" t="s">
         <v>767</v>
       </c>
-      <c r="B332" s="37" t="s">
-        <v>99</v>
+      <c r="B332" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C332" s="37"/>
       <c r="D332" s="85"/>
@@ -7210,30 +8049,44 @@
       <c r="A334" s="40" t="s">
         <v>769</v>
       </c>
-      <c r="B334" s="37" t="s">
-        <v>99</v>
+      <c r="B334" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C334" s="37"/>
-      <c r="D334" s="85"/>
+      <c r="D334" s="85" t="inlineStr">
+        <is>
+          <t>Có lịch sử phiếu kho theo Dự án; thiếu báo cáo cấp phát tổng hợp.</t>
+        </is>
+      </c>
       <c r="E334" s="86"/>
     </row>
     <row r="335">
       <c r="A335" s="40" t="s">
         <v>770</v>
       </c>
-      <c r="B335" s="37" t="s">
-        <v>99</v>
+      <c r="B335" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C335" s="37"/>
-      <c r="D335" s="85"/>
+      <c r="D335" s="85" t="inlineStr">
+        <is>
+          <t>Có cảnh báo Over-BOQ; thiếu báo cáo sử dụng toàn bộ vật tư so với BOQ.</t>
+        </is>
+      </c>
       <c r="E335" s="86"/>
     </row>
     <row r="336">
       <c r="A336" s="40" t="s">
         <v>771</v>
       </c>
-      <c r="B336" s="37" t="s">
-        <v>99</v>
+      <c r="B336" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C336" s="37"/>
       <c r="D336" s="44"/>
@@ -7243,8 +8096,10 @@
       <c r="A337" s="40" t="s">
         <v>772</v>
       </c>
-      <c r="B337" s="37" t="s">
-        <v>99</v>
+      <c r="B337" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C337" s="37"/>
       <c r="D337" s="97"/>
@@ -7254,8 +8109,10 @@
       <c r="A338" s="40" t="s">
         <v>773</v>
       </c>
-      <c r="B338" s="37" t="s">
-        <v>99</v>
+      <c r="B338" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C338" s="37"/>
       <c r="D338" s="97"/>
@@ -7265,22 +8122,34 @@
       <c r="A339" s="40" t="s">
         <v>774</v>
       </c>
-      <c r="B339" s="37" t="s">
-        <v>99</v>
+      <c r="B339" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C339" s="37"/>
-      <c r="D339" s="97"/>
+      <c r="D339" s="97" t="inlineStr">
+        <is>
+          <t>Có lọc phiếu kho/cảnh báo; thiếu báo cáo cung ứng tổng hợp theo vật tư.</t>
+        </is>
+      </c>
       <c r="E339" s="98"/>
     </row>
     <row r="340">
       <c r="A340" s="40" t="s">
         <v>775</v>
       </c>
-      <c r="B340" s="37" t="s">
-        <v>99</v>
+      <c r="B340" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C340" s="37"/>
-      <c r="D340" s="85"/>
+      <c r="D340" s="85" t="inlineStr">
+        <is>
+          <t>Có CSV phiếu kho/cảnh báo; thiếu xuất báo cáo cung ứng tổng hợp.</t>
+        </is>
+      </c>
       <c r="E340" s="86"/>
     </row>
     <row r="341">
@@ -7296,8 +8165,10 @@
       <c r="A342" s="40" t="s">
         <v>575</v>
       </c>
-      <c r="B342" s="37" t="s">
-        <v>99</v>
+      <c r="B342" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C342" s="37"/>
       <c r="D342" s="85"/>
@@ -7307,8 +8178,10 @@
       <c r="A343" s="40" t="s">
         <v>777</v>
       </c>
-      <c r="B343" s="37" t="s">
-        <v>99</v>
+      <c r="B343" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C343" s="37"/>
       <c r="D343" s="85"/>
@@ -7318,8 +8191,10 @@
       <c r="A344" s="40" t="s">
         <v>778</v>
       </c>
-      <c r="B344" s="37" t="s">
-        <v>99</v>
+      <c r="B344" s="37" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
       <c r="C344" s="37"/>
       <c r="D344" s="44"/>
@@ -7329,8 +8204,10 @@
       <c r="A345" s="40" t="s">
         <v>779</v>
       </c>
-      <c r="B345" s="37" t="s">
-        <v>99</v>
+      <c r="B345" s="37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="C345" s="37"/>
       <c r="D345" s="97"/>
@@ -7340,33 +8217,51 @@
       <c r="A346" s="40" t="s">
         <v>780</v>
       </c>
-      <c r="B346" s="37" t="s">
-        <v>99</v>
+      <c r="B346" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C346" s="37"/>
-      <c r="D346" s="97"/>
+      <c r="D346" s="97" t="inlineStr">
+        <is>
+          <t>Có trạng thái QA/QC; thiếu notification riêng cho nghiệm thu không đạt.</t>
+        </is>
+      </c>
       <c r="E346" s="98"/>
     </row>
     <row r="347">
       <c r="A347" s="40" t="s">
         <v>781</v>
       </c>
-      <c r="B347" s="37" t="s">
-        <v>99</v>
+      <c r="B347" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C347" s="37"/>
-      <c r="D347" s="97"/>
+      <c r="D347" s="97" t="inlineStr">
+        <is>
+          <t>Có cảnh báo từng module; thiếu risk register tập trung theo Dự án.</t>
+        </is>
+      </c>
       <c r="E347" s="98"/>
     </row>
     <row r="348">
       <c r="A348" s="40" t="s">
         <v>782</v>
       </c>
-      <c r="B348" s="37" t="s">
-        <v>99</v>
+      <c r="B348" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
       <c r="C348" s="37"/>
-      <c r="D348" s="85"/>
+      <c r="D348" s="85" t="inlineStr">
+        <is>
+          <t>Có dashboard vận hành; thiếu tổng hợp cảnh báo liên module và drill-down nguồn.</t>
+        </is>
+      </c>
       <c r="E348" s="86"/>
     </row>
     <row r="349">
@@ -10123,8 +11018,8 @@
     <mergeCell ref="A187:D187"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B13:B17 B19:B23 B25:B26 B28:B41 B43:B51 B53:B64 B67:B74 B76:B83 B85:B92 B94:B100 B102:B108 B111:B118 B120:B127 B130:B138 B140:B149 B151:B159 B161:C168 B170:C176 B178:C186 B189:C195 B197:C204 B206:C212 B214:C219 B221:C227 B229:C235 B237:C242 B245:C253 B255:C262 B264:C271 B273:C279 B281:C287 B290:C297 B299:C307 B310:C316 B318:C324 B326:C332 B334:C340 B342:C348">
-      <formula1>Nicon!$J$24:$J$27</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4:B5 B7 B9:B10 B13:B17 B19:B23 B25:B26 B28:B41 B43:B51 B53:B64 B67:B74 B76:B83 B85:B92 B94:B100 B102:B108 B111:B118 B120:B127 B130:B138 B140:B149 B151:B159 B161:C168 B170:C176 B178:C186 B189:C195 B197:C204 B206:C212 B214:C219 B221:C227 B229:C235 B237:C242 B245:C253 B255:C262 B264:C271 B273:C279 B281:C287 B290:C297 B299:C307 B310:C316 B318:C324 B326:C332 B334:C340 B342:C348">
+      <formula1>Nicon!$J$24:$J$26</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -10594,7 +11489,7 @@
     <col customWidth="1" min="3" max="3" width="21.86"/>
     <col customWidth="1" min="4" max="4" width="32.43"/>
     <col customWidth="1" min="5" max="5" width="73.71"/>
-    <col customWidth="1" min="6" max="6" width="25.43"/>
+    <col customWidth="1" min="6" max="6" width="62.0"/>
     <col customWidth="1" min="7" max="7" width="18.0"/>
     <col customWidth="1" min="8" max="8" width="18.43"/>
   </cols>
@@ -10645,8 +11540,10 @@
         <v>26</v>
       </c>
       <c r="G2" s="17"/>
-      <c r="H2" s="25" t="s">
-        <v>28</v>
+      <c r="H2" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -10665,8 +11562,10 @@
         <v>33</v>
       </c>
       <c r="G3" s="17"/>
-      <c r="H3" s="25" t="s">
-        <v>28</v>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -10685,8 +11584,10 @@
         <v>38</v>
       </c>
       <c r="G4" s="17"/>
-      <c r="H4" s="25" t="s">
-        <v>28</v>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -10707,8 +11608,10 @@
         <v>26</v>
       </c>
       <c r="G5" s="17"/>
-      <c r="H5" s="25" t="s">
-        <v>28</v>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -10727,8 +11630,10 @@
         <v>33</v>
       </c>
       <c r="G6" s="17"/>
-      <c r="H6" s="25" t="s">
-        <v>28</v>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -10747,8 +11652,10 @@
         <v>38</v>
       </c>
       <c r="G7" s="17"/>
-      <c r="H7" s="25" t="s">
-        <v>28</v>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -10767,8 +11674,10 @@
         <v>54</v>
       </c>
       <c r="G8" s="17"/>
-      <c r="H8" s="25" t="s">
-        <v>28</v>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -10789,8 +11698,10 @@
         <v>26</v>
       </c>
       <c r="G9" s="17"/>
-      <c r="H9" s="25" t="s">
-        <v>28</v>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -10809,11 +11720,13 @@
         <v>33</v>
       </c>
       <c r="G10" s="17"/>
-      <c r="H10" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="17">
         <v>10.0</v>
       </c>
@@ -10825,12 +11738,16 @@
       <c r="E11" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>38</v>
+      <c r="F11" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu xuất PDF báo giá; đã có XLSX và gửi khách hàng có preview.</t>
+        </is>
       </c>
       <c r="G11" s="17"/>
-      <c r="H11" s="25" t="s">
-        <v>28</v>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -10851,8 +11768,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="17"/>
-      <c r="H12" s="25" t="s">
-        <v>28</v>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -10871,8 +11790,10 @@
         <v>33</v>
       </c>
       <c r="G13" s="17"/>
-      <c r="H13" s="25" t="s">
-        <v>28</v>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -10891,8 +11812,10 @@
         <v>38</v>
       </c>
       <c r="G14" s="17"/>
-      <c r="H14" s="25" t="s">
-        <v>28</v>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -10911,8 +11834,10 @@
         <v>83</v>
       </c>
       <c r="G15" s="17"/>
-      <c r="H15" s="25" t="s">
-        <v>28</v>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -10933,8 +11858,10 @@
         <v>26</v>
       </c>
       <c r="G16" s="17"/>
-      <c r="H16" s="25" t="s">
-        <v>28</v>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -10953,8 +11880,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="17"/>
-      <c r="H17" s="25" t="s">
-        <v>28</v>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -10973,8 +11902,10 @@
         <v>38</v>
       </c>
       <c r="G18" s="17"/>
-      <c r="H18" s="25" t="s">
-        <v>28</v>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -10995,8 +11926,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="17"/>
-      <c r="H19" s="25" t="s">
-        <v>28</v>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -11015,8 +11948,10 @@
         <v>33</v>
       </c>
       <c r="G20" s="17"/>
-      <c r="H20" s="25" t="s">
-        <v>28</v>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -11035,8 +11970,10 @@
         <v>38</v>
       </c>
       <c r="G21" s="17"/>
-      <c r="H21" s="25" t="s">
-        <v>28</v>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -11059,8 +11996,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="17"/>
-      <c r="H22" s="25" t="s">
-        <v>28</v>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -11079,8 +12018,10 @@
         <v>33</v>
       </c>
       <c r="G23" s="17"/>
-      <c r="H23" s="25" t="s">
-        <v>28</v>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -11099,8 +12040,10 @@
         <v>38</v>
       </c>
       <c r="G24" s="17"/>
-      <c r="H24" s="25" t="s">
-        <v>28</v>
+      <c r="H24" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -11121,8 +12064,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="17"/>
-      <c r="H25" s="25" t="s">
-        <v>28</v>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -11141,11 +12086,13 @@
         <v>33</v>
       </c>
       <c r="G26" s="17"/>
-      <c r="H26" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="17">
         <v>26.0</v>
       </c>
@@ -11157,12 +12104,16 @@
       <c r="E27" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>38</v>
+      <c r="F27" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu trình duyệt/ký trực tiếp trên portal khách hàng và markup từng file.</t>
+        </is>
       </c>
       <c r="G27" s="17"/>
-      <c r="H27" s="25" t="s">
-        <v>28</v>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -11183,8 +12134,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="17"/>
-      <c r="H28" s="25" t="s">
-        <v>28</v>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -11203,8 +12156,10 @@
         <v>33</v>
       </c>
       <c r="G29" s="17"/>
-      <c r="H29" s="25" t="s">
-        <v>28</v>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -11223,8 +12178,10 @@
         <v>38</v>
       </c>
       <c r="G30" s="17"/>
-      <c r="H30" s="25" t="s">
-        <v>28</v>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -11245,8 +12202,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="17"/>
-      <c r="H31" s="25" t="s">
-        <v>28</v>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -11265,11 +12224,13 @@
         <v>33</v>
       </c>
       <c r="G32" s="17"/>
-      <c r="H32" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="H32" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="17">
         <v>32.0</v>
       </c>
@@ -11281,12 +12242,16 @@
       <c r="E33" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="F33" s="17" t="s">
-        <v>38</v>
+      <c r="F33" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu markup/review chéo trực tiếp trên từng file bản vẽ.</t>
+        </is>
       </c>
       <c r="G33" s="17"/>
-      <c r="H33" s="25" t="s">
-        <v>28</v>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -11307,8 +12272,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="17"/>
-      <c r="H34" s="25" t="s">
-        <v>28</v>
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -11327,8 +12294,10 @@
         <v>33</v>
       </c>
       <c r="G35" s="17"/>
-      <c r="H35" s="25" t="s">
-        <v>28</v>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -11347,8 +12316,10 @@
         <v>38</v>
       </c>
       <c r="G36" s="17"/>
-      <c r="H36" s="25" t="s">
-        <v>28</v>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -11369,8 +12340,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="17"/>
-      <c r="H37" s="25" t="s">
-        <v>28</v>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -11389,11 +12362,13 @@
         <v>33</v>
       </c>
       <c r="G38" s="17"/>
-      <c r="H38" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
       <c r="A39" s="17">
         <v>38.0</v>
       </c>
@@ -11405,12 +12380,16 @@
       <c r="E39" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>38</v>
+      <c r="F39" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu đóng dấu điện tử trên file bản vẽ IFC.</t>
+        </is>
       </c>
       <c r="G39" s="17"/>
-      <c r="H39" s="25" t="s">
-        <v>28</v>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -11433,8 +12412,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="17"/>
-      <c r="H40" s="25" t="s">
-        <v>240</v>
+      <c r="H40" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -11453,8 +12434,10 @@
         <v>33</v>
       </c>
       <c r="G41" s="17"/>
-      <c r="H41" s="25" t="s">
-        <v>240</v>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -11473,8 +12456,10 @@
         <v>38</v>
       </c>
       <c r="G42" s="17"/>
-      <c r="H42" s="25" t="s">
-        <v>240</v>
+      <c r="H42" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -11497,8 +12482,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="17"/>
-      <c r="H43" s="25" t="s">
-        <v>240</v>
+      <c r="H43" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -11517,11 +12504,13 @@
         <v>33</v>
       </c>
       <c r="G44" s="17"/>
-      <c r="H44" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="H44" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
       <c r="A45" s="17">
         <v>44.0</v>
       </c>
@@ -11533,12 +12522,16 @@
       <c r="E45" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="F45" s="17" t="s">
-        <v>259</v>
+      <c r="F45" s="103" t="inlineStr">
+        <is>
+          <t>Detail page + Gantt UI | Thiếu baseline WBS/S-Curve, critical path và cảnh báo lệch &gt;5%.</t>
+        </is>
       </c>
       <c r="G45" s="17"/>
-      <c r="H45" s="25" t="s">
-        <v>240</v>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -11559,8 +12552,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="17"/>
-      <c r="H46" s="25" t="s">
-        <v>240</v>
+      <c r="H46" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -11579,11 +12574,13 @@
         <v>33</v>
       </c>
       <c r="G47" s="17"/>
-      <c r="H47" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
       <c r="A48" s="17">
         <v>47.0</v>
       </c>
@@ -11595,12 +12592,16 @@
       <c r="E48" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="F48" s="17" t="s">
-        <v>38</v>
+      <c r="F48" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu ảnh/video đính kèm chuyên dụng và chữ ký xác nhận số.</t>
+        </is>
       </c>
       <c r="G48" s="17"/>
-      <c r="H48" s="25" t="s">
-        <v>240</v>
+      <c r="H48" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -11621,8 +12622,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="17"/>
-      <c r="H49" s="25" t="s">
-        <v>240</v>
+      <c r="H49" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -11641,11 +12644,13 @@
         <v>33</v>
       </c>
       <c r="G50" s="17"/>
-      <c r="H50" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="H50" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
       <c r="A51" s="17">
         <v>50.0</v>
       </c>
@@ -11657,12 +12662,16 @@
       <c r="E51" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="F51" s="17" t="s">
-        <v>38</v>
+      <c r="F51" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu checklist nghiệm thu NICON và kết quả Đạt/Không đạt riêng.</t>
+        </is>
       </c>
       <c r="G51" s="17"/>
-      <c r="H51" s="25" t="s">
-        <v>282</v>
+      <c r="H51" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -11683,8 +12692,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="17"/>
-      <c r="H52" s="25" t="s">
-        <v>282</v>
+      <c r="H52" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -11703,11 +12714,13 @@
         <v>33</v>
       </c>
       <c r="G53" s="17"/>
-      <c r="H53" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="H53" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
       <c r="A54" s="17">
         <v>53.0</v>
       </c>
@@ -11719,12 +12732,16 @@
       <c r="E54" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="F54" s="17" t="s">
-        <v>38</v>
+      <c r="F54" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu checklist commissioning và gate bàn giao đủ hồ sơ ba bên.</t>
+        </is>
       </c>
       <c r="G54" s="17"/>
-      <c r="H54" s="25" t="s">
-        <v>282</v>
+      <c r="H54" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -11745,8 +12762,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="17"/>
-      <c r="H55" s="25" t="s">
-        <v>282</v>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -11765,11 +12784,13 @@
         <v>33</v>
       </c>
       <c r="G56" s="17"/>
-      <c r="H56" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="H56" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
       <c r="A57" s="17">
         <v>56.0</v>
       </c>
@@ -11781,12 +12802,16 @@
       <c r="E57" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="F57" s="17" t="s">
-        <v>38</v>
+      <c r="F57" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Có checklist/CSV; thiếu tự tổng hợp bản vẽ, biên bản và xuất trọn bộ tệp.</t>
+        </is>
       </c>
       <c r="G57" s="17"/>
-      <c r="H57" s="25" t="s">
-        <v>282</v>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -11807,8 +12832,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="17"/>
-      <c r="H58" s="25" t="s">
-        <v>282</v>
+      <c r="H58" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -11827,11 +12854,13 @@
         <v>33</v>
       </c>
       <c r="G59" s="17"/>
-      <c r="H59" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
       <c r="A60" s="17">
         <v>59.0</v>
       </c>
@@ -11843,12 +12872,16 @@
       <c r="E60" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="F60" s="17" t="s">
-        <v>38</v>
+      <c r="F60" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Thiếu ảnh/video attachment chuyên dụng và pin trên mặt bằng.</t>
+        </is>
       </c>
       <c r="G60" s="17"/>
-      <c r="H60" s="25" t="s">
-        <v>282</v>
+      <c r="H60" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -11871,8 +12904,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="17"/>
-      <c r="H61" s="25" t="s">
-        <v>282</v>
+      <c r="H61" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -11891,8 +12926,10 @@
         <v>33</v>
       </c>
       <c r="G62" s="17"/>
-      <c r="H62" s="25" t="s">
-        <v>282</v>
+      <c r="H62" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -11911,8 +12948,10 @@
         <v>38</v>
       </c>
       <c r="G63" s="17"/>
-      <c r="H63" s="25" t="s">
-        <v>282</v>
+      <c r="H63" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -11933,8 +12972,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="17"/>
-      <c r="H64" s="25" t="s">
-        <v>282</v>
+      <c r="H64" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -11953,8 +12994,10 @@
         <v>33</v>
       </c>
       <c r="G65" s="17"/>
-      <c r="H65" s="25" t="s">
-        <v>282</v>
+      <c r="H65" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -11973,8 +13016,10 @@
         <v>38</v>
       </c>
       <c r="G66" s="17"/>
-      <c r="H66" s="25" t="s">
-        <v>282</v>
+      <c r="H66" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -11995,11 +13040,13 @@
         <v>26</v>
       </c>
       <c r="G67" s="17"/>
-      <c r="H67" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="H67" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
       <c r="A68" s="17">
         <v>67.0</v>
       </c>
@@ -12011,12 +13058,16 @@
       <c r="E68" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>33</v>
+      <c r="F68" s="103" t="inlineStr">
+        <is>
+          <t>Create/Edit form | Thiếu import đa sheet giữ hierarchy, provenance, công thức và tổng hợp đối soát.</t>
+        </is>
       </c>
       <c r="G68" s="17"/>
-      <c r="H68" s="25" t="s">
-        <v>282</v>
+      <c r="H68" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -12035,8 +13086,10 @@
         <v>38</v>
       </c>
       <c r="G69" s="17"/>
-      <c r="H69" s="25" t="s">
-        <v>282</v>
+      <c r="H69" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -12057,8 +13110,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="17"/>
-      <c r="H70" s="25" t="s">
-        <v>282</v>
+      <c r="H70" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -12077,8 +13132,10 @@
         <v>33</v>
       </c>
       <c r="G71" s="17"/>
-      <c r="H71" s="25" t="s">
-        <v>282</v>
+      <c r="H71" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -12097,8 +13154,10 @@
         <v>38</v>
       </c>
       <c r="G72" s="17"/>
-      <c r="H72" s="25" t="s">
-        <v>282</v>
+      <c r="H72" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -12119,8 +13178,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="17"/>
-      <c r="H73" s="25" t="s">
-        <v>282</v>
+      <c r="H73" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -12139,11 +13200,13 @@
         <v>33</v>
       </c>
       <c r="G74" s="17"/>
-      <c r="H74" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="H74" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
       <c r="A75" s="17">
         <v>74.0</v>
       </c>
@@ -12155,12 +13218,16 @@
       <c r="E75" s="23" t="s">
         <v>436</v>
       </c>
-      <c r="F75" s="17" t="s">
-        <v>38</v>
+      <c r="F75" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Có phiếu kho/cấp phát; thiếu quy trình kiểm kê kho độc lập.</t>
+        </is>
       </c>
       <c r="G75" s="17"/>
-      <c r="H75" s="25" t="s">
-        <v>282</v>
+      <c r="H75" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -12181,8 +13248,10 @@
         <v>448</v>
       </c>
       <c r="G76" s="17"/>
-      <c r="H76" s="25" t="s">
-        <v>282</v>
+      <c r="H76" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -12205,8 +13274,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="17"/>
-      <c r="H77" s="25" t="s">
-        <v>282</v>
+      <c r="H77" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -12225,11 +13296,13 @@
         <v>33</v>
       </c>
       <c r="G78" s="17"/>
-      <c r="H78" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="79">
+      <c r="H78" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
       <c r="A79" s="17">
         <v>78.0</v>
       </c>
@@ -12241,12 +13314,16 @@
       <c r="E79" s="23" t="s">
         <v>464</v>
       </c>
-      <c r="F79" s="17" t="s">
-        <v>38</v>
+      <c r="F79" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Có Hợp đồng/mốc/VO; thiếu sổ phải thu và thu tiền đối soát chứng từ.</t>
+        </is>
       </c>
       <c r="G79" s="17"/>
-      <c r="H79" s="25" t="s">
-        <v>282</v>
+      <c r="H79" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -12267,8 +13344,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="17"/>
-      <c r="H80" s="25" t="s">
-        <v>282</v>
+      <c r="H80" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -12287,11 +13366,13 @@
         <v>33</v>
       </c>
       <c r="G81" s="17"/>
-      <c r="H81" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="H81" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
       <c r="A82" s="17">
         <v>81.0</v>
       </c>
@@ -12303,12 +13384,16 @@
       <c r="E82" s="23" t="s">
         <v>474</v>
       </c>
-      <c r="F82" s="17" t="s">
-        <v>38</v>
+      <c r="F82" s="103" t="inlineStr">
+        <is>
+          <t>Detail page | Có Hợp đồng/mốc/Payment Request; thiếu sổ phải trả và dossier thanh toán.</t>
+        </is>
       </c>
       <c r="G82" s="17"/>
-      <c r="H82" s="25" t="s">
-        <v>282</v>
+      <c r="H82" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -12329,8 +13414,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="17"/>
-      <c r="H83" s="25" t="s">
-        <v>282</v>
+      <c r="H83" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -12349,8 +13436,10 @@
         <v>33</v>
       </c>
       <c r="G84" s="17"/>
-      <c r="H84" s="25" t="s">
-        <v>282</v>
+      <c r="H84" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -12369,8 +13458,10 @@
         <v>38</v>
       </c>
       <c r="G85" s="17"/>
-      <c r="H85" s="25" t="s">
-        <v>282</v>
+      <c r="H85" s="25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -12391,8 +13482,10 @@
         <v>489</v>
       </c>
       <c r="G86" s="17"/>
-      <c r="H86" s="25" t="s">
-        <v>282</v>
+      <c r="H86" s="25" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -12413,11 +13506,13 @@
         <v>494</v>
       </c>
       <c r="G87" s="17"/>
-      <c r="H87" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="88">
+      <c r="H87" s="25" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
       <c r="A88" s="17">
         <v>87.0</v>
       </c>
@@ -12433,15 +13528,19 @@
       <c r="E88" s="23" t="s">
         <v>499</v>
       </c>
-      <c r="F88" s="17" t="s">
-        <v>500</v>
+      <c r="F88" s="103" t="inlineStr">
+        <is>
+          <t>Setting + Integration | Có folder cấu hình/sync; thiếu topology Survey dưới CRM Pre-Design đã migration.</t>
+        </is>
       </c>
       <c r="G88" s="17"/>
-      <c r="H88" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="89" ht="50.25" customHeight="1">
+      <c r="H88" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
       <c r="A89" s="17">
         <v>88.0</v>
       </c>
@@ -12455,15 +13554,19 @@
       <c r="E89" s="23" t="s">
         <v>505</v>
       </c>
-      <c r="F89" s="17" t="s">
-        <v>506</v>
+      <c r="F89" s="103" t="inlineStr">
+        <is>
+          <t>Repository page | Có catalog tìm kiếm/phân quyền; thiếu tree view thư mục thống nhất.</t>
+        </is>
       </c>
       <c r="G89" s="17"/>
-      <c r="H89" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="H89" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
       <c r="A90" s="17">
         <v>89.0</v>
       </c>
@@ -12479,15 +13582,19 @@
       <c r="E90" s="23" t="s">
         <v>510</v>
       </c>
-      <c r="F90" s="17" t="s">
-        <v>315</v>
+      <c r="F90" s="103" t="inlineStr">
+        <is>
+          <t>Dashboard | Có dashboard vận hành; thiếu tài chính thực tế, tồn kho và KPI đủ 11 vị trí.</t>
+        </is>
       </c>
       <c r="G90" s="17"/>
-      <c r="H90" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="91" ht="46.5" customHeight="1">
+      <c r="H90" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
       <c r="A91" s="17">
         <v>90.0</v>
       </c>
@@ -12501,15 +13608,19 @@
       <c r="E91" s="23" t="s">
         <v>514</v>
       </c>
-      <c r="F91" s="17" t="s">
-        <v>494</v>
+      <c r="F91" s="103" t="inlineStr">
+        <is>
+          <t>Report | Có báo cáo Dự án; thiếu số liệu tài chính, BOQ usage và vendor performance.</t>
+        </is>
       </c>
       <c r="G91" s="17"/>
-      <c r="H91" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="H91" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
       <c r="A92" s="17">
         <v>91.0</v>
       </c>
@@ -12523,17 +13634,21 @@
       <c r="E92" s="77" t="s">
         <v>289</v>
       </c>
-      <c r="F92" s="77" t="s">
-        <v>291</v>
+      <c r="F92" s="103" t="inlineStr">
+        <is>
+          <t>Setting + CRUD | Có cấu hình 6 nhóm KPI; thiếu framework đủ 11 vị trí NICON.</t>
+        </is>
       </c>
       <c r="G92" s="78" t="s">
         <v>517</v>
       </c>
-      <c r="H92" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="93">
+      <c r="H92" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
       <c r="A93" s="17">
         <v>92.0</v>
       </c>
@@ -12545,17 +13660,21 @@
       <c r="E93" s="77" t="s">
         <v>298</v>
       </c>
-      <c r="F93" s="77" t="s">
-        <v>299</v>
+      <c r="F93" s="103" t="inlineStr">
+        <is>
+          <t>Integration/rule config | Có mapping nguồn cho 19 chỉ số; thiếu nguồn/rule cho các vị trí còn lại.</t>
+        </is>
       </c>
       <c r="G93" s="79">
         <v>46145.0</v>
       </c>
-      <c r="H93" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="94">
+      <c r="H93" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
       <c r="A94" s="17">
         <v>93.0</v>
       </c>
@@ -12567,17 +13686,21 @@
       <c r="E94" s="77" t="s">
         <v>306</v>
       </c>
-      <c r="F94" s="77" t="s">
-        <v>307</v>
+      <c r="F94" s="103" t="inlineStr">
+        <is>
+          <t>Backend service | Có engine và khóa kỳ; thiếu chỉ số đầy đủ cho 11 vị trí.</t>
+        </is>
       </c>
       <c r="G94" s="78" t="s">
         <v>520</v>
       </c>
-      <c r="H94" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="95">
+      <c r="H94" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
       <c r="A95" s="17">
         <v>94.0</v>
       </c>
@@ -12589,17 +13712,21 @@
       <c r="E95" s="77" t="s">
         <v>312</v>
       </c>
-      <c r="F95" s="77" t="s">
-        <v>315</v>
+      <c r="F95" s="103" t="inlineStr">
+        <is>
+          <t>Dashboard | Có dashboard KPI theo nhân viên/kỳ; thiếu toàn bộ 11 vị trí và drill-down biến động đầy đủ.</t>
+        </is>
       </c>
       <c r="G95" s="78" t="s">
         <v>522</v>
       </c>
-      <c r="H95" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="H95" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
       <c r="A96" s="17">
         <v>95.0</v>
       </c>
@@ -12611,17 +13738,21 @@
       <c r="E96" s="77" t="s">
         <v>322</v>
       </c>
-      <c r="F96" s="77" t="s">
-        <v>324</v>
+      <c r="F96" s="103" t="inlineStr">
+        <is>
+          <t>Report + Export | Có export KPI hiện tại; thiếu Google Sheets/PDF theo toàn bộ vị trí.</t>
+        </is>
       </c>
       <c r="G96" s="79">
         <v>46144.0</v>
       </c>
-      <c r="H96" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="97">
+      <c r="H96" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
       <c r="A97" s="17">
         <v>96.0</v>
       </c>
@@ -12633,17 +13764,21 @@
       <c r="E97" s="77" t="s">
         <v>329</v>
       </c>
-      <c r="F97" s="77" t="s">
-        <v>331</v>
+      <c r="F97" s="103" t="inlineStr">
+        <is>
+          <t>Workflow/admin | Có khóa kỳ/snapshot; thiếu phạm vi HR/Admin theo framework NICON.</t>
+        </is>
       </c>
       <c r="G97" s="79">
         <v>46144.0</v>
       </c>
-      <c r="H97" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="98">
+      <c r="H97" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
       <c r="A98" s="17">
         <v>97.0</v>
       </c>
@@ -12655,17 +13790,21 @@
       <c r="E98" s="77" t="s">
         <v>344</v>
       </c>
-      <c r="F98" s="77" t="s">
-        <v>347</v>
+      <c r="F98" s="103" t="inlineStr">
+        <is>
+          <t>Notification/audit | Có audit KPI/export; thiếu cảnh báo điểm bất thường theo rule đã duyệt.</t>
+        </is>
       </c>
       <c r="G98" s="79">
         <v>46143.0</v>
       </c>
-      <c r="H98" s="25" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="H98" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
       <c r="A99" s="17">
         <v>98.0</v>
       </c>
@@ -12681,15 +13820,19 @@
       <c r="E99" s="23" t="s">
         <v>530</v>
       </c>
-      <c r="F99" s="88" t="s">
-        <v>4</v>
+      <c r="F99" s="103" t="inlineStr">
+        <is>
+          <t>Chức năng chung | Có workflow cho một số hồ sơ; thiếu cấu hình approval matrix chung cho mọi loại.</t>
+        </is>
       </c>
       <c r="G99" s="17"/>
-      <c r="H99" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="H99" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
       <c r="A100" s="17">
         <v>99.0</v>
       </c>
@@ -12705,15 +13848,19 @@
       <c r="E100" s="23" t="s">
         <v>534</v>
       </c>
-      <c r="F100" s="88" t="s">
-        <v>4</v>
+      <c r="F100" s="103" t="inlineStr">
+        <is>
+          <t>Chức năng chung | Có role/permission editor; thiếu mapping 11 vị trí theo cơ cấu NICON chốt.</t>
+        </is>
       </c>
       <c r="G100" s="17"/>
-      <c r="H100" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="H100" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
       <c r="A101" s="17">
         <v>100.0</v>
       </c>
@@ -12729,12 +13876,16 @@
       <c r="E101" s="23" t="s">
         <v>538</v>
       </c>
-      <c r="F101" s="88" t="s">
-        <v>4</v>
+      <c r="F101" s="103" t="inlineStr">
+        <is>
+          <t>Chức năng chung | Có notification in-app/email theo sự kiện; thiếu phủ đầy đủ mọi luồng nghiệp vụ.</t>
+        </is>
       </c>
       <c r="G101" s="17"/>
-      <c r="H101" s="25" t="s">
-        <v>28</v>
+      <c r="H101" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -12757,11 +13908,13 @@
         <v>4</v>
       </c>
       <c r="G102" s="17"/>
-      <c r="H102" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="103">
+      <c r="H102" s="25" t="inlineStr">
+        <is>
+          <t>Not Implement</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
       <c r="A103" s="17">
         <v>102.0</v>
       </c>
@@ -12777,15 +13930,19 @@
       <c r="E103" s="23" t="s">
         <v>547</v>
       </c>
-      <c r="F103" s="88" t="s">
-        <v>4</v>
+      <c r="F103" s="103" t="inlineStr">
+        <is>
+          <t>Chức năng chung | Có audit log; thiếu phủ mọi thao tác tải file và toàn bộ luồng quan trọng.</t>
+        </is>
       </c>
       <c r="G103" s="17"/>
-      <c r="H103" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="104">
+      <c r="H103" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
       <c r="A104" s="17">
         <v>103.0</v>
       </c>
@@ -12801,12 +13958,16 @@
       <c r="E104" s="23" t="s">
         <v>552</v>
       </c>
-      <c r="F104" s="88" t="s">
-        <v>4</v>
+      <c r="F104" s="103" t="inlineStr">
+        <is>
+          <t>Chức năng chung | Có master data dùng chung; thiếu template/checklist theo dự án và approval matrix NICON.</t>
+        </is>
       </c>
       <c r="G104" s="17"/>
-      <c r="H104" s="25" t="s">
-        <v>28</v>
+      <c r="H104" s="25" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -12829,8 +13990,10 @@
         <v>559</v>
       </c>
       <c r="G105" s="93"/>
-      <c r="H105" s="89" t="s">
-        <v>28</v>
+      <c r="H105" s="89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -12853,8 +14016,10 @@
         <v>559</v>
       </c>
       <c r="G106" s="93"/>
-      <c r="H106" s="89" t="s">
-        <v>28</v>
+      <c r="H106" s="89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -12877,8 +14042,10 @@
         <v>559</v>
       </c>
       <c r="G107" s="93"/>
-      <c r="H107" s="89" t="s">
-        <v>28</v>
+      <c r="H107" s="89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -12901,8 +14068,10 @@
         <v>559</v>
       </c>
       <c r="G108" s="93"/>
-      <c r="H108" s="89" t="s">
-        <v>28</v>
+      <c r="H108" s="89" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -16756,7 +17925,7 @@
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H108">
-      <formula1>"Done,In Progress,Not Implement"</formula1>
+      <formula1>"Done,Partial,Not Implement"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4032,20 +4032,18 @@
       <c r="E31" s="49"/>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="s">
-        <v>157</v>
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Xuất file Excel / Gửi khách hàng</t>
+        </is>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C32" s="37"/>
-      <c r="D32" s="48" t="inlineStr">
-        <is>
-          <t>Thiếu xuất PDF báo giá; đã có XLSX và gửi email có preview.</t>
-        </is>
-      </c>
+      <c r="D32" s="48"/>
       <c r="E32" s="49"/>
     </row>
     <row r="33">
@@ -11726,7 +11724,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11">
       <c r="A11" s="17">
         <v>10.0</v>
       </c>
@@ -11735,18 +11733,18 @@
       <c r="D11" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="103" t="inlineStr">
-        <is>
-          <t>Detail page | Thiếu xuất PDF báo giá; đã có XLSX và gửi khách hàng có preview.</t>
-        </is>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Thông tin báo giá, version, duyệt nội bộ, in/xuất Excel</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4195,20 +4195,18 @@
       <c r="E44" s="39"/>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="s">
-        <v>229</v>
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Upload video khảo sát hiện trạng</t>
+        </is>
       </c>
       <c r="B45" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C45" s="37"/>
-      <c r="D45" s="44" t="inlineStr">
-        <is>
-          <t>Đã upload video; thiếu quay video trực tiếp trong ứng dụng.</t>
-        </is>
-      </c>
+      <c r="D45" s="48"/>
       <c r="E45" s="39"/>
     </row>
     <row r="46">

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C41" s="37"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4315,13 +4315,13 @@
       </c>
       <c r="B54" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C54" s="37"/>
       <c r="D54" s="48" t="inlineStr">
         <is>
-          <t>Hợp đồng gắn Opportunity/Báo giá/Dự án; thiếu liên kết Lead trực tiếp.</t>
+          <t>Truy vết Lead qua Cơ hội nguồn theo quyền Lead; giữ liên kết Báo giá/Dự án.</t>
         </is>
       </c>
       <c r="E54" s="49"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4358,13 +4358,13 @@
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C57" s="37"/>
       <c r="D57" s="48" t="inlineStr">
         <is>
-          <t>Có lifecycle hợp đồng; thiếu tiến độ thực hiện từ công việc/nghiệm thu.</t>
+          <t>Tách công việc/QS/thanh toán gắn Hợp đồng; có nguồn đối chiếu, không gộp %.</t>
         </is>
       </c>
       <c r="E57" s="49"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -3441,8 +3441,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghi chú — đối chiếu source d884b3c6, 20/10/2026; không xác nhận host/UAT</t>
+        </is>
       </c>
       <c r="E1" s="2"/>
     </row>
@@ -3516,7 +3518,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C4" s="4"/>
@@ -3552,7 +3554,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C5" s="4"/>
@@ -3620,7 +3622,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C7" s="4"/>
@@ -3688,7 +3690,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C9" s="4"/>
@@ -3724,7 +3726,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C10" s="4"/>
@@ -3780,7 +3782,7 @@
       </c>
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C13" s="37"/>
@@ -3793,7 +3795,7 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C14" s="37"/>
@@ -3806,7 +3808,7 @@
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C15" s="37"/>
@@ -3819,7 +3821,7 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C16" s="37"/>
@@ -3832,7 +3834,7 @@
       </c>
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C17" s="37"/>
@@ -3856,7 +3858,7 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C19" s="37"/>
@@ -3869,7 +3871,7 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C20" s="37"/>
@@ -3882,7 +3884,7 @@
       </c>
       <c r="B21" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C21" s="37"/>
@@ -3895,7 +3897,7 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C22" s="37"/>
@@ -3908,7 +3910,7 @@
       </c>
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C23" s="37"/>
@@ -3925,7 +3927,7 @@
       <c r="E24" s="39"/>
       <c r="J24" s="43" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3937,7 @@
       </c>
       <c r="B25" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C25" s="37"/>
@@ -3953,7 +3955,7 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C26" s="37"/>
@@ -3961,7 +3963,7 @@
       <c r="E26" s="39"/>
       <c r="J26" s="43" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3977,7 @@
       <c r="E27" s="39"/>
       <c r="J27" s="43" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Open decision</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3987,7 @@
       </c>
       <c r="B28" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C28" s="37"/>
@@ -3998,7 +4000,7 @@
       </c>
       <c r="B29" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C29" s="37"/>
@@ -4011,7 +4013,7 @@
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C30" s="37"/>
@@ -4024,7 +4026,7 @@
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C31" s="37"/>
@@ -4039,7 +4041,7 @@
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C32" s="37"/>
@@ -4052,7 +4054,7 @@
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C33" s="37"/>
@@ -4074,7 +4076,7 @@
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C35" s="37"/>
@@ -4087,7 +4089,7 @@
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C36" s="37"/>
@@ -4100,7 +4102,7 @@
       </c>
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C37" s="37"/>
@@ -4113,7 +4115,7 @@
       </c>
       <c r="B38" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C38" s="37"/>
@@ -4126,7 +4128,7 @@
       </c>
       <c r="B39" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C39" s="37"/>
@@ -4139,7 +4141,7 @@
       </c>
       <c r="B40" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C40" s="37"/>
@@ -4152,7 +4154,7 @@
       </c>
       <c r="B41" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C41" s="37"/>
@@ -4174,7 +4176,7 @@
       </c>
       <c r="B43" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C43" s="37"/>
@@ -4187,7 +4189,7 @@
       </c>
       <c r="B44" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C44" s="37"/>
@@ -4202,7 +4204,7 @@
       </c>
       <c r="B45" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C45" s="37"/>
@@ -4215,7 +4217,7 @@
       </c>
       <c r="B46" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C46" s="37"/>
@@ -4228,7 +4230,7 @@
       </c>
       <c r="B47" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C47" s="37"/>
@@ -4241,7 +4243,7 @@
       </c>
       <c r="B48" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C48" s="37"/>
@@ -4254,7 +4256,7 @@
       </c>
       <c r="B49" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C49" s="37"/>
@@ -4267,7 +4269,7 @@
       </c>
       <c r="B50" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C50" s="37"/>
@@ -4280,7 +4282,7 @@
       </c>
       <c r="B51" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C51" s="37"/>
@@ -4302,7 +4304,7 @@
       </c>
       <c r="B53" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C53" s="37"/>
@@ -4315,7 +4317,7 @@
       </c>
       <c r="B54" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C54" s="37"/>
@@ -4332,7 +4334,7 @@
       </c>
       <c r="B55" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C55" s="37"/>
@@ -4345,7 +4347,7 @@
       </c>
       <c r="B56" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C56" s="37"/>
@@ -4358,7 +4360,7 @@
       </c>
       <c r="B57" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C57" s="37"/>
@@ -4375,7 +4377,7 @@
       </c>
       <c r="B58" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C58" s="37"/>
@@ -4388,7 +4390,7 @@
       </c>
       <c r="B59" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C59" s="37"/>
@@ -4401,7 +4403,7 @@
       </c>
       <c r="B60" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C60" s="37"/>
@@ -4431,13 +4433,13 @@
       </c>
       <c r="B62" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="48" t="inlineStr">
         <is>
-          <t>Có lịch sử chăm sóc Khách hàng; thiếu timeline riêng theo Hợp đồng.</t>
+          <t xml:space="preserve">Timeline riêng theo HĐ; phân quyền, phân trang, retry; có lịch sử thì khóa đổi chiều.</t>
         </is>
       </c>
       <c r="E62" s="49"/>
@@ -4448,7 +4450,7 @@
       </c>
       <c r="B63" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C63" s="37"/>
@@ -4461,7 +4463,7 @@
       </c>
       <c r="B64" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C64" s="37"/>
@@ -4492,7 +4494,7 @@
       </c>
       <c r="B67" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C67" s="37"/>
@@ -4539,7 +4541,7 @@
       </c>
       <c r="B70" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C70" s="37"/>
@@ -4558,7 +4560,7 @@
       <c r="C71" s="37"/>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>Có quyết định/yêu cầu chỉnh sửa; thiếu thread phản hồi theo từng file của khách hàng.</t>
+          <t xml:space="preserve">Có bình luận nội bộ gắn từng file và ghi nhận ý kiến khách; chưa có thread/markup trực tiếp của khách.</t>
         </is>
       </c>
       <c r="E71" s="39"/>
@@ -4603,7 +4605,7 @@
       </c>
       <c r="B74" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C74" s="37"/>
@@ -4625,7 +4627,7 @@
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C76" s="37"/>
@@ -4638,7 +4640,7 @@
       </c>
       <c r="B77" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C77" s="37"/>
@@ -4651,7 +4653,7 @@
       </c>
       <c r="B78" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C78" s="37"/>
@@ -4664,7 +4666,7 @@
       </c>
       <c r="B79" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C79" s="37"/>
@@ -4677,7 +4679,7 @@
       </c>
       <c r="B80" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C80" s="37"/>
@@ -4690,7 +4692,7 @@
       </c>
       <c r="B81" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C81" s="37"/>
@@ -4703,7 +4705,7 @@
       </c>
       <c r="B82" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C82" s="37"/>
@@ -4716,7 +4718,7 @@
       </c>
       <c r="B83" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C83" s="37"/>
@@ -4738,7 +4740,7 @@
       </c>
       <c r="B85" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C85" s="37"/>
@@ -4751,7 +4753,7 @@
       </c>
       <c r="B86" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C86" s="37"/>
@@ -4764,7 +4766,7 @@
       </c>
       <c r="B87" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C87" s="37"/>
@@ -4777,7 +4779,7 @@
       </c>
       <c r="B88" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C88" s="37"/>
@@ -4807,7 +4809,7 @@
       </c>
       <c r="B90" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C90" s="37"/>
@@ -4820,7 +4822,7 @@
       </c>
       <c r="B91" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C91" s="37"/>
@@ -4833,7 +4835,7 @@
       </c>
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C92" s="37"/>
@@ -4855,7 +4857,7 @@
       </c>
       <c r="B94" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C94" s="37"/>
@@ -4885,11 +4887,15 @@
       </c>
       <c r="B96" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Partial</t>
         </is>
       </c>
       <c r="C96" s="37"/>
-      <c r="D96" s="44"/>
+      <c r="D96" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có so sánh metadata hai revision cùng bản vẽ; chưa so sánh nội dung/đồ họa của file.</t>
+        </is>
+      </c>
       <c r="E96" s="39"/>
     </row>
     <row r="97">
@@ -4898,7 +4904,7 @@
       </c>
       <c r="B97" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C97" s="37"/>
@@ -4911,7 +4917,7 @@
       </c>
       <c r="B98" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C98" s="37"/>
@@ -4924,7 +4930,7 @@
       </c>
       <c r="B99" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C99" s="37"/>
@@ -4937,11 +4943,15 @@
       </c>
       <c r="B100" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C100" s="37"/>
-      <c r="D100" s="44"/>
+      <c r="D100" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có lịch sử revision/IFC; chưa có luồng thông báo khi cập nhật revision cho các bộ phận.</t>
+        </is>
+      </c>
       <c r="E100" s="39"/>
     </row>
     <row r="101">
@@ -4959,7 +4969,7 @@
       </c>
       <c r="B102" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C102" s="37"/>
@@ -4989,7 +4999,7 @@
       </c>
       <c r="B104" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C104" s="37"/>
@@ -5002,7 +5012,7 @@
       </c>
       <c r="B105" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C105" s="37"/>
@@ -5015,7 +5025,7 @@
       </c>
       <c r="B106" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C106" s="37"/>
@@ -5028,7 +5038,7 @@
       </c>
       <c r="B107" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C107" s="37"/>
@@ -5041,7 +5051,7 @@
       </c>
       <c r="B108" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C108" s="37"/>
@@ -5072,7 +5082,7 @@
       </c>
       <c r="B111" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C111" s="37"/>
@@ -5085,7 +5095,7 @@
       </c>
       <c r="B112" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C112" s="37"/>
@@ -5104,7 +5114,7 @@
       <c r="C113" s="37"/>
       <c r="D113" s="80" t="inlineStr">
         <is>
-          <t>Có checklist theo dự án; thiếu template bắt buộc theo loại/quy mô công trình.</t>
+          <t xml:space="preserve">Có checklist theo Dự án; CM/NICON chưa duyệt template bắt buộc theo loại/quy mô công trình.</t>
         </is>
       </c>
       <c r="E113" s="81"/>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="B114" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C114" s="37"/>
@@ -5128,7 +5138,7 @@
       </c>
       <c r="B115" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C115" s="37"/>
@@ -5141,7 +5151,7 @@
       </c>
       <c r="B116" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C116" s="37"/>
@@ -5154,7 +5164,7 @@
       </c>
       <c r="B117" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C117" s="37"/>
@@ -5167,7 +5177,7 @@
       </c>
       <c r="B118" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C118" s="37"/>
@@ -5189,7 +5199,7 @@
       </c>
       <c r="B120" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C120" s="37"/>
@@ -5202,7 +5212,7 @@
       </c>
       <c r="B121" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C121" s="37"/>
@@ -5215,7 +5225,7 @@
       </c>
       <c r="B122" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C122" s="37"/>
@@ -5228,7 +5238,7 @@
       </c>
       <c r="B123" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C123" s="37"/>
@@ -5241,7 +5251,7 @@
       </c>
       <c r="B124" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C124" s="37"/>
@@ -5254,7 +5264,7 @@
       </c>
       <c r="B125" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C125" s="37"/>
@@ -5267,7 +5277,7 @@
       </c>
       <c r="B126" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C126" s="37"/>
@@ -5280,7 +5290,7 @@
       </c>
       <c r="B127" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C127" s="37"/>
@@ -5345,7 +5355,7 @@
       </c>
       <c r="B132" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C132" s="37"/>
@@ -5358,7 +5368,7 @@
       </c>
       <c r="B133" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C133" s="37"/>
@@ -5371,7 +5381,7 @@
       </c>
       <c r="B134" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C134" s="37"/>
@@ -5384,7 +5394,7 @@
       </c>
       <c r="B135" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C135" s="37"/>
@@ -5431,7 +5441,7 @@
       </c>
       <c r="B138" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C138" s="37"/>
@@ -5453,7 +5463,7 @@
       </c>
       <c r="B140" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C140" s="37"/>
@@ -5466,7 +5476,7 @@
       </c>
       <c r="B141" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C141" s="37"/>
@@ -5513,7 +5523,7 @@
       </c>
       <c r="B144" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C144" s="37"/>
@@ -5526,7 +5536,7 @@
       </c>
       <c r="B145" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C145" s="37"/>
@@ -5539,7 +5549,7 @@
       </c>
       <c r="B146" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C146" s="37"/>
@@ -5552,7 +5562,7 @@
       </c>
       <c r="B147" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C147" s="37"/>
@@ -5565,7 +5575,7 @@
       </c>
       <c r="B148" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C148" s="37"/>
@@ -5578,7 +5588,7 @@
       </c>
       <c r="B149" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C149" s="37"/>
@@ -5600,7 +5610,7 @@
       </c>
       <c r="B151" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C151" s="37"/>
@@ -5613,7 +5623,7 @@
       </c>
       <c r="B152" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C152" s="37"/>
@@ -5632,7 +5642,7 @@
       <c r="C153" s="37"/>
       <c r="D153" s="99" t="inlineStr">
         <is>
-          <t>Có dữ liệu QA/QC; thiếu checklist nghiệm thu bắt buộc theo template NICON.</t>
+          <t xml:space="preserve">Có template engine QA/QC; còn chờ CM duyệt mapping/checklist ISO NICON để publish mẫu sản xuất.</t>
         </is>
       </c>
       <c r="E153" s="86"/>
@@ -5643,7 +5653,7 @@
       </c>
       <c r="B154" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C154" s="37"/>
@@ -5656,7 +5666,7 @@
       </c>
       <c r="B155" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C155" s="37"/>
@@ -5686,7 +5696,7 @@
       </c>
       <c r="B157" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C157" s="37"/>
@@ -5699,7 +5709,7 @@
       </c>
       <c r="B158" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C158" s="37"/>
@@ -5712,7 +5722,7 @@
       </c>
       <c r="B159" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C159" s="37"/>
@@ -5785,7 +5795,7 @@
       </c>
       <c r="B164" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C164" s="37"/>
@@ -5815,7 +5825,7 @@
       </c>
       <c r="B166" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C166" s="37"/>
@@ -5828,7 +5838,7 @@
       </c>
       <c r="B167" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C167" s="37"/>
@@ -5841,7 +5851,7 @@
       </c>
       <c r="B168" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C168" s="37"/>
@@ -5863,7 +5873,7 @@
       </c>
       <c r="B170" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C170" s="37"/>
@@ -5893,7 +5903,7 @@
       </c>
       <c r="B172" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C172" s="37"/>
@@ -5906,7 +5916,7 @@
       </c>
       <c r="B173" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C173" s="37"/>
@@ -5936,7 +5946,7 @@
       </c>
       <c r="B175" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C175" s="37"/>
@@ -5949,7 +5959,7 @@
       </c>
       <c r="B176" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C176" s="37"/>
@@ -5971,7 +5981,7 @@
       </c>
       <c r="B178" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C178" s="37"/>
@@ -5984,7 +5994,7 @@
       </c>
       <c r="B179" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C179" s="37"/>
@@ -6014,7 +6024,7 @@
       </c>
       <c r="B181" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C181" s="37"/>
@@ -6027,7 +6037,7 @@
       </c>
       <c r="B182" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C182" s="37"/>
@@ -6040,7 +6050,7 @@
       </c>
       <c r="B183" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C183" s="37"/>
@@ -6053,7 +6063,7 @@
       </c>
       <c r="B184" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C184" s="37"/>
@@ -6066,7 +6076,7 @@
       </c>
       <c r="B185" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C185" s="37"/>
@@ -6079,7 +6089,7 @@
       </c>
       <c r="B186" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C186" s="37"/>
@@ -6110,7 +6120,7 @@
       </c>
       <c r="B189" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C189" s="37"/>
@@ -6123,7 +6133,7 @@
       </c>
       <c r="B190" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C190" s="37"/>
@@ -6136,7 +6146,7 @@
       </c>
       <c r="B191" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C191" s="37"/>
@@ -6149,7 +6159,7 @@
       </c>
       <c r="B192" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C192" s="37"/>
@@ -6179,7 +6189,7 @@
       </c>
       <c r="B194" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C194" s="37"/>
@@ -6192,7 +6202,7 @@
       </c>
       <c r="B195" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C195" s="37"/>
@@ -6231,7 +6241,7 @@
       </c>
       <c r="B198" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C198" s="37"/>
@@ -6244,7 +6254,7 @@
       </c>
       <c r="B199" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C199" s="37"/>
@@ -6257,7 +6267,7 @@
       </c>
       <c r="B200" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C200" s="37"/>
@@ -6270,7 +6280,7 @@
       </c>
       <c r="B201" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C201" s="37"/>
@@ -6283,7 +6293,7 @@
       </c>
       <c r="B202" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C202" s="37"/>
@@ -6296,7 +6306,7 @@
       </c>
       <c r="B203" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C203" s="37"/>
@@ -6309,7 +6319,7 @@
       </c>
       <c r="B204" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C204" s="37"/>
@@ -6348,7 +6358,7 @@
       </c>
       <c r="B207" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C207" s="37"/>
@@ -6361,7 +6371,7 @@
       </c>
       <c r="B208" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C208" s="37"/>
@@ -6374,7 +6384,7 @@
       </c>
       <c r="B209" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C209" s="37"/>
@@ -6387,7 +6397,7 @@
       </c>
       <c r="B210" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C210" s="37"/>
@@ -6400,7 +6410,7 @@
       </c>
       <c r="B211" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C211" s="37"/>
@@ -6456,7 +6466,7 @@
       </c>
       <c r="B215" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C215" s="37"/>
@@ -6469,7 +6479,7 @@
       </c>
       <c r="B216" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C216" s="37"/>
@@ -6499,7 +6509,7 @@
       </c>
       <c r="B218" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C218" s="37"/>
@@ -6512,7 +6522,7 @@
       </c>
       <c r="B219" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C219" s="37"/>
@@ -6551,7 +6561,7 @@
       </c>
       <c r="B222" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C222" s="37"/>
@@ -6564,7 +6574,7 @@
       </c>
       <c r="B223" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C223" s="37"/>
@@ -6577,7 +6587,7 @@
       </c>
       <c r="B224" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C224" s="37"/>
@@ -6590,7 +6600,7 @@
       </c>
       <c r="B225" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C225" s="37"/>
@@ -6603,7 +6613,7 @@
       </c>
       <c r="B226" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C226" s="37"/>
@@ -6616,7 +6626,7 @@
       </c>
       <c r="B227" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C227" s="37"/>
@@ -6672,7 +6682,7 @@
       </c>
       <c r="B231" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C231" s="37"/>
@@ -6685,7 +6695,7 @@
       </c>
       <c r="B232" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C232" s="37"/>
@@ -6698,7 +6708,7 @@
       </c>
       <c r="B233" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C233" s="37"/>
@@ -6728,7 +6738,7 @@
       </c>
       <c r="B235" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C235" s="37"/>
@@ -6750,7 +6760,7 @@
       </c>
       <c r="B237" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C237" s="37"/>
@@ -6763,7 +6773,7 @@
       </c>
       <c r="B238" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C238" s="37"/>
@@ -6793,7 +6803,7 @@
       </c>
       <c r="B240" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C240" s="37"/>
@@ -6806,7 +6816,7 @@
       </c>
       <c r="B241" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C241" s="37"/>
@@ -6819,7 +6829,7 @@
       </c>
       <c r="B242" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C242" s="37"/>
@@ -6850,7 +6860,7 @@
       </c>
       <c r="B245" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C245" s="37"/>
@@ -6863,7 +6873,7 @@
       </c>
       <c r="B246" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C246" s="37"/>
@@ -6876,7 +6886,7 @@
       </c>
       <c r="B247" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C247" s="37"/>
@@ -6895,7 +6905,7 @@
       <c r="C248" s="37"/>
       <c r="D248" s="30" t="inlineStr">
         <is>
-          <t>Có mốc thanh toán; thiếu gate theo nghiệm thu/QS được duyệt.</t>
+          <t xml:space="preserve">Có mốc phải thu và tham chiếu QS Upstream; chưa có dossier/gate thu tiền theo ISO đã duyệt.</t>
         </is>
       </c>
       <c r="E248" s="101"/>
@@ -6923,7 +6933,7 @@
       </c>
       <c r="B250" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C250" s="37"/>
@@ -6936,7 +6946,7 @@
       </c>
       <c r="B251" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C251" s="37"/>
@@ -6949,7 +6959,7 @@
       </c>
       <c r="B252" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C252" s="37"/>
@@ -6962,7 +6972,7 @@
       </c>
       <c r="B253" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C253" s="37"/>
@@ -6984,7 +6994,7 @@
       </c>
       <c r="B255" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C255" s="37"/>
@@ -6997,7 +7007,7 @@
       </c>
       <c r="B256" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C256" s="37"/>
@@ -7010,7 +7020,7 @@
       </c>
       <c r="B257" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C257" s="37"/>
@@ -7029,7 +7039,7 @@
       <c r="C258" s="37"/>
       <c r="D258" s="30" t="inlineStr">
         <is>
-          <t>Có mốc thanh toán Downstream; thiếu liên kết tiến độ/QS đủ điều kiện.</t>
+          <t xml:space="preserve">Có mốc Downstream và QS liên kết Payment Request; chưa có gate ISO cho từng loại gói.</t>
         </is>
       </c>
       <c r="E258" s="101"/>
@@ -7040,7 +7050,7 @@
       </c>
       <c r="B259" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C259" s="37"/>
@@ -7059,7 +7069,7 @@
       <c r="C260" s="37"/>
       <c r="D260" s="30" t="inlineStr">
         <is>
-          <t>Có lifecycle hợp đồng; thiếu tiến độ thi công thực tế theo gói thầu.</t>
+          <t xml:space="preserve">Có nguồn công việc, QS và mốc thanh toán theo HĐ; chưa có % tiến độ gói thầu theo baseline.</t>
         </is>
       </c>
       <c r="E260" s="101"/>
@@ -7076,7 +7086,7 @@
       <c r="C261" s="37"/>
       <c r="D261" s="30" t="inlineStr">
         <is>
-          <t>Có Payment Request/Paid; thiếu lịch sử chi tiền có chứng từ đối soát.</t>
+          <t xml:space="preserve">Có Payment Request/Paid, lịch sử revision và sửa hồ sơ khi QS bị thay thế; thiếu sổ chi đối soát.</t>
         </is>
       </c>
       <c r="E261" s="101"/>
@@ -7087,7 +7097,7 @@
       </c>
       <c r="B262" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C262" s="37"/>
@@ -7109,7 +7119,7 @@
       </c>
       <c r="B264" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C264" s="37"/>
@@ -7139,7 +7149,7 @@
       </c>
       <c r="B266" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C266" s="37"/>
@@ -7158,7 +7168,7 @@
       <c r="C267" s="37"/>
       <c r="D267" s="30" t="inlineStr">
         <is>
-          <t>VO hiện gắn Hợp đồng Upstream; thiếu VO cho Hợp đồng Downstream.</t>
+          <t xml:space="preserve">API/UI VO dùng chung theo HĐ; chưa có test riêng xác nhận đầy đủ luồng VO Downstream.</t>
         </is>
       </c>
       <c r="E267" s="101"/>
@@ -7169,7 +7179,7 @@
       </c>
       <c r="B268" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C268" s="37"/>
@@ -7182,7 +7192,7 @@
       </c>
       <c r="B269" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C269" s="37"/>
@@ -7195,7 +7205,7 @@
       </c>
       <c r="B270" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C270" s="37"/>
@@ -7208,7 +7218,7 @@
       </c>
       <c r="B271" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C271" s="37"/>
@@ -7264,7 +7274,7 @@
       </c>
       <c r="B275" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C275" s="37"/>
@@ -7311,7 +7321,7 @@
       </c>
       <c r="B278" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C278" s="37"/>
@@ -7324,7 +7334,7 @@
       </c>
       <c r="B279" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C279" s="37"/>
@@ -7346,7 +7356,7 @@
       </c>
       <c r="B281" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C281" s="37"/>
@@ -7359,7 +7369,7 @@
       </c>
       <c r="B282" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C282" s="37"/>
@@ -7372,7 +7382,7 @@
       </c>
       <c r="B283" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C283" s="37"/>
@@ -7385,11 +7395,15 @@
       </c>
       <c r="B284" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C284" s="37"/>
-      <c r="D284" s="30"/>
+      <c r="D284" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CM có giá trị QS được duyệt/kỳ nghiệm thu; chưa có nguồn chi phí thực tế và công thức so với dự toán.</t>
+        </is>
+      </c>
       <c r="E284" s="101"/>
     </row>
     <row r="285">
@@ -7398,7 +7412,7 @@
       </c>
       <c r="B285" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C285" s="37"/>
@@ -7411,7 +7425,7 @@
       </c>
       <c r="B286" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C286" s="37"/>
@@ -7424,7 +7438,7 @@
       </c>
       <c r="B287" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C287" s="37"/>
@@ -7455,7 +7469,7 @@
       </c>
       <c r="B290" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C290" s="37"/>
@@ -7485,7 +7499,7 @@
       </c>
       <c r="B292" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C292" s="37"/>
@@ -7498,7 +7512,7 @@
       </c>
       <c r="B293" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C293" s="37"/>
@@ -7545,7 +7559,7 @@
       </c>
       <c r="B296" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C296" s="37"/>
@@ -7558,7 +7572,7 @@
       </c>
       <c r="B297" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C297" s="37"/>
@@ -7580,7 +7594,7 @@
       </c>
       <c r="B299" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C299" s="37"/>
@@ -7593,7 +7607,7 @@
       </c>
       <c r="B300" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C300" s="37"/>
@@ -7606,7 +7620,7 @@
       </c>
       <c r="B301" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C301" s="37"/>
@@ -7619,7 +7633,7 @@
       </c>
       <c r="B302" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C302" s="37"/>
@@ -7632,7 +7646,7 @@
       </c>
       <c r="B303" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C303" s="37"/>
@@ -7645,7 +7659,7 @@
       </c>
       <c r="B304" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C304" s="37"/>
@@ -7658,7 +7672,7 @@
       </c>
       <c r="B305" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C305" s="37"/>
@@ -7671,7 +7685,7 @@
       </c>
       <c r="B306" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C306" s="37"/>
@@ -7684,7 +7698,7 @@
       </c>
       <c r="B307" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C307" s="37"/>
@@ -7721,7 +7735,7 @@
       <c r="C310" s="37"/>
       <c r="D310" s="85" t="inlineStr">
         <is>
-          <t>Có tiến độ thiết kế và đếm task thi công; thiếu % thi công theo baseline.</t>
+          <t xml:space="preserve">Có task/Gantt và CM theo trạng thái hiện tại; chưa có % thi công theo baseline đã công bố.</t>
         </is>
       </c>
       <c r="E310" s="86"/>
@@ -7749,7 +7763,7 @@
       </c>
       <c r="B312" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C312" s="37"/>
@@ -7779,7 +7793,7 @@
       </c>
       <c r="B314" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C314" s="37"/>
@@ -7792,7 +7806,7 @@
       </c>
       <c r="B315" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C315" s="37"/>
@@ -7805,7 +7819,7 @@
       </c>
       <c r="B316" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C316" s="37"/>
@@ -7833,7 +7847,7 @@
       <c r="C318" s="37"/>
       <c r="D318" s="85" t="inlineStr">
         <is>
-          <t>Có số lượng nghiệm thu; thiếu tỷ lệ đạt/không đạt có mẫu số chuẩn.</t>
+          <t xml:space="preserve">Có đếm nghiệm thu/QS riêng hai chiều; số hồ sơ không phải tỷ lệ hay khối lượng vật lý hoàn thành.</t>
         </is>
       </c>
       <c r="E318" s="86"/>
@@ -7844,7 +7858,7 @@
       </c>
       <c r="B319" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C319" s="37"/>
@@ -7857,7 +7871,7 @@
       </c>
       <c r="B320" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C320" s="37"/>
@@ -7876,7 +7890,7 @@
       <c r="C321" s="37"/>
       <c r="D321" s="97" t="inlineStr">
         <is>
-          <t>Có file nghiệm thu theo hồ sơ; thiếu danh mục tổng hợp biên bản theo Dự án.</t>
+          <t xml:space="preserve">CM có nguồn QA/QC và link đối chiếu; chưa tự tập hợp đầy đủ biên bản nghiệm thu của Dự án.</t>
         </is>
       </c>
       <c r="E321" s="98"/>
@@ -7947,7 +7961,7 @@
       </c>
       <c r="B326" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C326" s="37"/>
@@ -7960,11 +7974,15 @@
       </c>
       <c r="B327" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Partial</t>
         </is>
       </c>
       <c r="C327" s="37"/>
-      <c r="D327" s="85"/>
+      <c r="D327" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có lịch mốc phải thu, ngày xác nhận thu và quá hạn; chưa có sổ phải thu đối soát chứng từ.</t>
+        </is>
+      </c>
       <c r="E327" s="86"/>
     </row>
     <row r="328">
@@ -7973,7 +7991,7 @@
       </c>
       <c r="B328" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C328" s="37"/>
@@ -7986,7 +8004,7 @@
       </c>
       <c r="B329" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C329" s="37"/>
@@ -7999,7 +8017,7 @@
       </c>
       <c r="B330" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C330" s="37"/>
@@ -8012,7 +8030,7 @@
       </c>
       <c r="B331" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C331" s="37"/>
@@ -8025,11 +8043,15 @@
       </c>
       <c r="B332" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Partial</t>
         </is>
       </c>
       <c r="C332" s="37"/>
-      <c r="D332" s="85"/>
+      <c r="D332" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có xuất báo cáo giá trị HĐ/mốc thanh toán; chưa xuất sổ thu–chi/P&amp;L thực tế.</t>
+        </is>
+      </c>
       <c r="E332" s="86"/>
     </row>
     <row r="333">
@@ -8081,7 +8103,7 @@
       </c>
       <c r="B336" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C336" s="37"/>
@@ -8094,7 +8116,7 @@
       </c>
       <c r="B337" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C337" s="37"/>
@@ -8107,7 +8129,7 @@
       </c>
       <c r="B338" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C338" s="37"/>
@@ -8163,7 +8185,7 @@
       </c>
       <c r="B342" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C342" s="37"/>
@@ -8176,7 +8198,7 @@
       </c>
       <c r="B343" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C343" s="37"/>
@@ -8189,7 +8211,7 @@
       </c>
       <c r="B344" s="37" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
       <c r="C344" s="37"/>
@@ -8202,7 +8224,7 @@
       </c>
       <c r="B345" s="37" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C345" s="37"/>
@@ -8255,7 +8277,7 @@
       <c r="C348" s="37"/>
       <c r="D348" s="85" t="inlineStr">
         <is>
-          <t>Có dashboard vận hành; thiếu tổng hợp cảnh báo liên module và drill-down nguồn.</t>
+          <t xml:space="preserve">Có dashboard và CM: QS hai chiều, giá trị/kỳ, QA/QC, HSE; còn thiếu tài chính thực tế và S-Curve.</t>
         </is>
       </c>
       <c r="E348" s="86"/>
@@ -11015,7 +11037,7 @@
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B4:B5 B7 B9:B10 B13:B17 B19:B23 B25:B26 B28:B41 B43:B51 B53:B64 B67:B74 B76:B83 B85:B92 B94:B100 B102:B108 B111:B118 B120:B127 B130:B138 B140:B149 B151:B159 B161:C168 B170:C176 B178:C186 B189:C195 B197:C204 B206:C212 B214:C219 B221:C227 B229:C235 B237:C242 B245:C253 B255:C262 B264:C271 B273:C279 B281:C287 B290:C297 B299:C307 B310:C316 B318:C324 B326:C332 B334:C340 B342:C348">
-      <formula1>Nicon!$J$24:$J$26</formula1>
+      <formula1>Nicon!$J$24:$J$27</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -11343,127 +11365,211 @@
       <c r="A2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="21"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="21"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="21"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="21"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="21"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="21"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="21"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="21"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="21"/>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="21"/>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="21"/>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="21"/>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="21"/>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -11506,8 +11612,10 @@
       <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>10</v>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghi chú — đối chiếu source d884b3c6, 20/10/2026</t>
+        </is>
       </c>
       <c r="G1" s="12" t="s">
         <v>12</v>
@@ -11538,7 +11646,7 @@
       <c r="G2" s="17"/>
       <c r="H2" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11668,7 @@
       <c r="G3" s="17"/>
       <c r="H3" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11690,7 @@
       <c r="G4" s="17"/>
       <c r="H4" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11714,7 @@
       <c r="G5" s="17"/>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11736,7 @@
       <c r="G6" s="17"/>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11758,7 @@
       <c r="G7" s="17"/>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11780,7 @@
       <c r="G8" s="17"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11804,7 @@
       <c r="G9" s="17"/>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11826,7 @@
       <c r="G10" s="17"/>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11850,7 @@
       <c r="G11" s="17"/>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11874,7 @@
       <c r="G12" s="17"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11788,7 +11896,7 @@
       <c r="G13" s="17"/>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11918,7 @@
       <c r="G14" s="17"/>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11940,7 @@
       <c r="G15" s="17"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11964,7 @@
       <c r="G16" s="17"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11986,7 @@
       <c r="G17" s="17"/>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11900,7 +12008,7 @@
       <c r="G18" s="17"/>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11924,7 +12032,7 @@
       <c r="G19" s="17"/>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11946,7 +12054,7 @@
       <c r="G20" s="17"/>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11962,13 +12070,15 @@
       <c r="E21" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>38</v>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có tiến độ theo HĐ, nguồn Lead và timeline chăm sóc riêng; có lịch sử thì khóa đổi chiều.</t>
+        </is>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12104,7 @@
       <c r="G22" s="17"/>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12126,7 @@
       <c r="G23" s="17"/>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12148,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12172,7 @@
       <c r="G25" s="17"/>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12194,7 @@
       <c r="G26" s="17"/>
       <c r="H26" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12102,7 +12212,7 @@
       </c>
       <c r="F27" s="103" t="inlineStr">
         <is>
-          <t>Detail page | Thiếu trình duyệt/ký trực tiếp trên portal khách hàng và markup từng file.</t>
+          <t xml:space="preserve">Có review nội bộ gắn file và ghi nhận quyết định khách; chưa có portal ký/markup trực tiếp.</t>
         </is>
       </c>
       <c r="G27" s="17"/>
@@ -12132,7 +12242,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12264,7 @@
       <c r="G29" s="17"/>
       <c r="H29" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12286,7 @@
       <c r="G30" s="17"/>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12310,7 @@
       <c r="G31" s="17"/>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12332,7 @@
       <c r="G32" s="17"/>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12350,7 @@
       </c>
       <c r="F33" s="103" t="inlineStr">
         <is>
-          <t>Detail page | Thiếu markup/review chéo trực tiếp trên từng file bản vẽ.</t>
+          <t xml:space="preserve">Có review nội bộ gắn file; chưa có markup đồ họa trực tiếp trên từng bản vẽ.</t>
         </is>
       </c>
       <c r="G33" s="17"/>
@@ -12270,7 +12380,7 @@
       <c r="G34" s="17"/>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12286,13 +12396,15 @@
       <c r="E35" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>33</v>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có tạo revision kèm lý do/ghi chú; chưa có sửa revision đã ghi nhận.</t>
+        </is>
       </c>
       <c r="G35" s="17"/>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Partial</t>
         </is>
       </c>
     </row>
@@ -12308,13 +12420,15 @@
       <c r="E36" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="F36" s="17" t="s">
-        <v>38</v>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Có lịch sử và so sánh metadata revision; chưa có diff nội dung file.</t>
+        </is>
       </c>
       <c r="G36" s="17"/>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12452,7 @@
       <c r="G37" s="17"/>
       <c r="H37" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12474,7 @@
       <c r="G38" s="17"/>
       <c r="H38" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12524,7 @@
       <c r="G40" s="17"/>
       <c r="H40" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12546,7 @@
       <c r="G41" s="17"/>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12568,7 @@
       <c r="G42" s="17"/>
       <c r="H42" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12594,7 @@
       <c r="G43" s="17"/>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12616,7 @@
       <c r="G44" s="17"/>
       <c r="H44" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12634,7 @@
       </c>
       <c r="F45" s="103" t="inlineStr">
         <is>
-          <t>Detail page + Gantt UI | Thiếu baseline WBS/S-Curve, critical path và cảnh báo lệch &gt;5%.</t>
+          <t xml:space="preserve">Có task/Gantt và readiness gate; thiếu baseline WBS/S-Curve có cấu trúc, critical path và lệch &gt;5%.</t>
         </is>
       </c>
       <c r="G45" s="17"/>
@@ -12550,7 +12664,7 @@
       <c r="G46" s="17"/>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12686,7 @@
       <c r="G47" s="17"/>
       <c r="H47" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12734,7 @@
       <c r="G49" s="17"/>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12756,7 @@
       <c r="G50" s="17"/>
       <c r="H50" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12774,7 @@
       </c>
       <c r="F51" s="103" t="inlineStr">
         <is>
-          <t>Detail page | Thiếu checklist nghiệm thu NICON và kết quả Đạt/Không đạt riêng.</t>
+          <t xml:space="preserve">Có QA/QC template engine, IFC/evidence; chờ CM duyệt mapping ISO, chưa đủ gate nghiệm thu mục tiêu.</t>
         </is>
       </c>
       <c r="G51" s="17"/>
@@ -12690,7 +12804,7 @@
       <c r="G52" s="17"/>
       <c r="H52" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12826,7 @@
       <c r="G53" s="17"/>
       <c r="H53" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12760,7 +12874,7 @@
       <c r="G55" s="17"/>
       <c r="H55" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12896,7 @@
       <c r="G56" s="17"/>
       <c r="H56" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12944,7 @@
       <c r="G58" s="17"/>
       <c r="H58" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12966,7 @@
       <c r="G59" s="17"/>
       <c r="H59" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12902,7 +13016,7 @@
       <c r="G61" s="17"/>
       <c r="H61" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12924,7 +13038,7 @@
       <c r="G62" s="17"/>
       <c r="H62" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12946,7 +13060,7 @@
       <c r="G63" s="17"/>
       <c r="H63" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12970,7 +13084,7 @@
       <c r="G64" s="17"/>
       <c r="H64" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -12992,7 +13106,7 @@
       <c r="G65" s="17"/>
       <c r="H65" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13128,7 @@
       <c r="G66" s="17"/>
       <c r="H66" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13152,7 @@
       <c r="G67" s="17"/>
       <c r="H67" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13198,7 @@
       <c r="G69" s="17"/>
       <c r="H69" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13222,7 @@
       <c r="G70" s="17"/>
       <c r="H70" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13244,7 @@
       <c r="G71" s="17"/>
       <c r="H71" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13266,7 @@
       <c r="G72" s="17"/>
       <c r="H72" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13290,7 @@
       <c r="G73" s="17"/>
       <c r="H73" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13312,7 @@
       <c r="G74" s="17"/>
       <c r="H74" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13360,7 @@
       <c r="G76" s="17"/>
       <c r="H76" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13272,7 +13386,7 @@
       <c r="G77" s="17"/>
       <c r="H77" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13408,7 @@
       <c r="G78" s="17"/>
       <c r="H78" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13426,7 @@
       </c>
       <c r="F79" s="103" t="inlineStr">
         <is>
-          <t>Detail page | Có Hợp đồng/mốc/VO; thiếu sổ phải thu và thu tiền đối soát chứng từ.</t>
+          <t xml:space="preserve">Có HĐ, mốc, ngày thu và VO; thiếu sổ phải thu đối soát chứng từ.</t>
         </is>
       </c>
       <c r="G79" s="17"/>
@@ -13342,7 +13456,7 @@
       <c r="G80" s="17"/>
       <c r="H80" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13478,7 @@
       <c r="G81" s="17"/>
       <c r="H81" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13496,7 @@
       </c>
       <c r="F82" s="103" t="inlineStr">
         <is>
-          <t>Detail page | Có Hợp đồng/mốc/Payment Request; thiếu sổ phải trả và dossier thanh toán.</t>
+          <t xml:space="preserve">Có Payment Request gắn QS Downstream, revision khôi phục; thiếu sổ phải trả và dossier ISO ba section.</t>
         </is>
       </c>
       <c r="G82" s="17"/>
@@ -13412,7 +13526,7 @@
       <c r="G83" s="17"/>
       <c r="H83" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13434,7 +13548,7 @@
       <c r="G84" s="17"/>
       <c r="H84" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13570,7 @@
       <c r="G85" s="17"/>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13594,7 @@
       <c r="G86" s="17"/>
       <c r="H86" s="25" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13618,7 @@
       <c r="G87" s="17"/>
       <c r="H87" s="25" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13694,7 @@
       </c>
       <c r="F90" s="103" t="inlineStr">
         <is>
-          <t>Dashboard | Có dashboard vận hành; thiếu tài chính thực tế, tồn kho và KPI đủ 11 vị trí.</t>
+          <t xml:space="preserve">Có dashboard vận hành và CM: QS hai chiều, giá trị/kỳ, QA/QC, HSE; thiếu ledger, S-Curve, đủ 11 vị trí.</t>
         </is>
       </c>
       <c r="G90" s="17"/>
@@ -13606,7 +13720,7 @@
       </c>
       <c r="F91" s="103" t="inlineStr">
         <is>
-          <t>Report | Có báo cáo Dự án; thiếu số liệu tài chính, BOQ usage và vendor performance.</t>
+          <t xml:space="preserve">Có báo cáo Dự án, nguồn CM và export; thiếu tài chính thực tế, BOQ usage và vendor performance.</t>
         </is>
       </c>
       <c r="G91" s="17"/>
@@ -13736,7 +13850,7 @@
       </c>
       <c r="F96" s="103" t="inlineStr">
         <is>
-          <t>Report + Export | Có export KPI hiện tại; thiếu Google Sheets/PDF theo toàn bộ vị trí.</t>
+          <t xml:space="preserve">Có CSV KPI theo nhân viên/kỳ; chưa có Google Sheets/PDF và lưu tự động lên Drive.</t>
         </is>
       </c>
       <c r="G96" s="79">
@@ -13762,7 +13876,7 @@
       </c>
       <c r="F97" s="103" t="inlineStr">
         <is>
-          <t>Workflow/admin | Có khóa kỳ/snapshot; thiếu phạm vi HR/Admin theo framework NICON.</t>
+          <t xml:space="preserve">Có khóa kỳ/snapshot và quyền manage; role HR mặc định chưa có quyền KPI.</t>
         </is>
       </c>
       <c r="G97" s="79">
@@ -13788,7 +13902,7 @@
       </c>
       <c r="F98" s="103" t="inlineStr">
         <is>
-          <t>Notification/audit | Có audit KPI/export; thiếu cảnh báo điểm bất thường theo rule đã duyệt.</t>
+          <t xml:space="preserve">Có audit/export và cảnh báo điểm thấp theo ngưỡng; chưa phủ rule/cảnh báo đủ 11 vị trí.</t>
         </is>
       </c>
       <c r="G98" s="79">
@@ -13906,7 +14020,7 @@
       <c r="G102" s="17"/>
       <c r="H102" s="25" t="inlineStr">
         <is>
-          <t>Not Implement</t>
+          <t xml:space="preserve">Target</t>
         </is>
       </c>
     </row>
@@ -13988,7 +14102,7 @@
       <c r="G105" s="93"/>
       <c r="H105" s="89" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -14014,7 +14128,7 @@
       <c r="G106" s="93"/>
       <c r="H106" s="89" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14154,7 @@
       <c r="G107" s="93"/>
       <c r="H107" s="89" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14180,7 @@
       <c r="G108" s="93"/>
       <c r="H108" s="89" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
     </row>
@@ -17921,7 +18035,7 @@
   </mergeCells>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H108">
-      <formula1>"Done,Partial,Not Implement"</formula1>
+      <formula1>"Implemented,Partial,Target,Open decision"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4416,13 +4416,13 @@
       </c>
       <c r="B61" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t xml:space="preserve">Implemented</t>
         </is>
       </c>
       <c r="C61" s="37"/>
       <c r="D61" s="48" t="inlineStr">
         <is>
-          <t>Có nhắc mốc thanh toán; thiếu nhắc gia hạn/kết thúc hợp đồng.</t>
+          <t xml:space="preserve">Email tự động theo ngày nhắc riêng; có xem trước, lịch sử gửi và mẫu tại /admin/email-templates.</t>
         </is>
       </c>
       <c r="E61" s="49"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -2503,7 +2503,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -2611,8 +2611,32 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2745,6 +2769,21 @@
         <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border/>
@@ -2823,10 +2862,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="116">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3100,6 +3140,40 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3431,7 +3505,7 @@
     <col customWidth="1" min="5" max="5" width="85.43"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1">
+    <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3441,9 +3515,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ghi chú — đối chiếu source d884b3c6, 20/10/2026; không xác nhận host/UAT</t>
+      <c r="D1" s="104" t="inlineStr">
+        <is>
+          <t>Ghi chú — đối chiếu source 7813bc5d, 21/10/2026; rà soát source/test hiện có, không chạy lại test, không xác nhận host/UAT</t>
         </is>
       </c>
       <c r="E1" s="2"/>
@@ -4410,7 +4484,7 @@
       <c r="D60" s="48"/>
       <c r="E60" s="49"/>
     </row>
-    <row r="61">
+    <row r="61" ht="78" customHeight="1">
       <c r="A61" s="44" t="s">
         <v>279</v>
       </c>
@@ -4420,14 +4494,14 @@
         </is>
       </c>
       <c r="C61" s="37"/>
-      <c r="D61" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Email tự động theo ngày nhắc riêng; có xem trước, lịch sử gửi và mẫu tại /admin/email-templates.</t>
+      <c r="D61" s="105" t="inlineStr">
+        <is>
+          <t>Upstream: chọn Renewal/End, ngày Việt Nam, người liên hệ → preview → xác nhận. Worker 5 phút/lần; mẫu tại /admin/email-templates; ghi chăm sóc sau SMTP. ContractReminderService/Worker; ContractRemindersTests; contract-reminder-email.spec.ts. Không tự gia hạn/đóng HĐ; Sending/NeedsReview cần đối soát, không tự retry.</t>
         </is>
       </c>
       <c r="E61" s="49"/>
     </row>
-    <row r="62">
+    <row r="62" ht="61" customHeight="1">
       <c r="A62" s="44" t="s">
         <v>283</v>
       </c>
@@ -4437,14 +4511,14 @@
         </is>
       </c>
       <c r="C62" s="37"/>
-      <c r="D62" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Timeline riêng theo HĐ; phân quyền, phân trang, retry; có lịch sử thì khóa đổi chiều.</t>
+      <c r="D62" s="105" t="inlineStr">
+        <is>
+          <t>Lịch sử chăm sóc riêng theo HĐ. Khóa đổi chiều sau lịch sử hoặc lần bắt đầu gửi email (AttemptedAt), kể cả SMTP chưa rõ kết quả. ContractService; ContractCareActivitiesTests; ContractRemindersTests.</t>
         </is>
       </c>
       <c r="E62" s="49"/>
     </row>
-    <row r="63">
+    <row r="63" ht="44" customHeight="1">
       <c r="A63" s="44" t="s">
         <v>290</v>
       </c>
@@ -4454,7 +4528,11 @@
         </is>
       </c>
       <c r="C63" s="37"/>
-      <c r="D63" s="48"/>
+      <c r="D63" s="105" t="inlineStr">
+        <is>
+          <t>Chưa thấy workflow tái ký/liên kết HĐ kế tiếp trong ContractService/ContractDetail. Email Renewal chỉ nhắc khách, không tạo/gia hạn HĐ mới.</t>
+        </is>
+      </c>
       <c r="E63" s="49"/>
     </row>
     <row r="64">
@@ -4501,36 +4579,36 @@
       <c r="D67" s="44"/>
       <c r="E67" s="39"/>
     </row>
-    <row r="68">
+    <row r="68" ht="61" customHeight="1">
       <c r="A68" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="B68" s="37" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="B68" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C68" s="37"/>
-      <c r="D68" s="44" t="inlineStr">
-        <is>
-          <t>Có lưu file thiết kế; thiếu quản lý/xem mô hình 3D chuyên dụng.</t>
+      <c r="D68" s="107" t="inlineStr">
+        <is>
+          <t>Quản lý file Model3D theo phương án/revision; tải bản gốc, ảnh/PDF có preview. ConceptDossierService.AddArtifactAsync; ConceptDossierPanel; admin-concept-dossier.spec.ts. Theo Nicon-QLVH §4, trình xem 3D chuyên dụng không là điều kiện hoàn thành.</t>
         </is>
       </c>
       <c r="E68" s="39"/>
     </row>
-    <row r="69">
+    <row r="69" ht="61" customHeight="1">
       <c r="A69" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="B69" s="37" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="B69" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C69" s="37"/>
-      <c r="D69" s="44" t="inlineStr">
-        <is>
-          <t>Có lưu bản vẽ Concept; thiếu quản lý mặt bằng công năng theo cấu trúc riêng.</t>
+      <c r="D69" s="107" t="inlineStr">
+        <is>
+          <t>FloorPlan có FloorLabel bắt buộc, tách SiteRoofPlan/Section; file đúng phương án/revision, sửa liên kết khi nháp. ConceptDossierService; ConceptDossierPanel; DesignReviewsControllerTests.ConceptDraft_CanCorrectFileAndWaiver_ButFrozenRevisionCannotChange.</t>
         </is>
       </c>
       <c r="E69" s="39"/>
@@ -4548,53 +4626,53 @@
       <c r="D70" s="44"/>
       <c r="E70" s="39"/>
     </row>
-    <row r="71">
+    <row r="71" ht="78" customHeight="1">
       <c r="A71" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B71" s="37" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="B71" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C71" s="37"/>
-      <c r="D71" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Có bình luận nội bộ gắn từng file và ghi nhận ý kiến khách; chưa có thread/markup trực tiếp của khách.</t>
+      <c r="D71" s="107" t="inlineStr">
+        <is>
+          <t>Ý kiến khách: nguyên văn, tên, kênh, thời điểm, nguồn bằng chứng, file; phản hồi/kết quả một lần. ConceptDossierService.AddFeedbackAsync/RespondAsync; ConceptDossierPanel; DesignReviewsControllerTests.ConceptDecision_RequiresSignedAcceptanceAndPreservesRejectedState. Markup đồ họa vẫn là Target riêng.</t>
         </is>
       </c>
       <c r="E71" s="39"/>
     </row>
-    <row r="72">
+    <row r="72" ht="78" customHeight="1">
       <c r="A72" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="B72" s="37" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="B72" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C72" s="37"/>
-      <c r="D72" s="44" t="inlineStr">
-        <is>
-          <t>Có nhiều phương án Concept; thiếu revision/version của cùng một phương án.</t>
+      <c r="D72" s="107" t="inlineStr">
+        <is>
+          <t>ConceptRevision R00/R01... theo cùng phương án; bản đã trình bất biến; revision mới sau yêu cầu sửa/từ chối. ConceptDossierService.CreateRevisionAsync; ConceptDossierPanel; DesignReviewsControllerTests.ClientChanges_CreateR01_PreservesR00AndRejectsIncompleteSubmission; ConceptDossierConcurrencyTests.</t>
         </is>
       </c>
       <c r="E72" s="39"/>
     </row>
-    <row r="73">
+    <row r="73" ht="78" customHeight="1">
       <c r="A73" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B73" s="37" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="B73" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C73" s="37"/>
-      <c r="D73" s="44" t="inlineStr">
-        <is>
-          <t>Có gate quyết định khách hàng; thiếu ký/chốt trực tiếp trên portal khách hàng.</t>
+      <c r="D73" s="107" t="inlineStr">
+        <is>
+          <t>Trình nội bộ → ghi nhận trình khách → ClientApproved kèm TK-M03 đã ký, người/ngày ký → chốt một phương án và mở Basic Design. ConceptOptionService; DesignReviewService; DesignReviewsTab; ConceptFinalizationPersistenceTests; ConceptOptionServiceTests. Không yêu cầu portal khách hàng theo Nicon-QLVH §4.</t>
         </is>
       </c>
       <c r="E73" s="39"/>
@@ -11351,27 +11429,38 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="218.0"/>
     <col customWidth="1" min="2" max="2" width="15.14"/>
+    <col min="3" max="3" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1">
+      <c r="C1" s="108" t="inlineStr">
+        <is>
+          <t>Đối chiếu source 7813bc5d, 21/10/2026; không chạy lại test, không xác nhận host/UAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="61" customHeight="1">
       <c r="A2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
+      <c r="B2" s="109" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C2" s="110" t="inlineStr">
+        <is>
+          <t>LeadService cho phép TaxId null; Leads.tsx không bắt MST khi convert. LeadsControllerTests.Convert_CompanyLeadWithoutTaxId_PreservesCustomerAndOpportunityLinks. Điều kiện pháp lý khi ký HĐ là gate khác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="19" t="s">
         <v>24</v>
       </c>
@@ -11380,8 +11469,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
+      <c r="C3" s="110" t="inlineStr">
+        <is>
+          <t>QuoteService cho phép cơ hội Won chưa có WonQuoteId tạo báo giá; chặn khi đã có báo giá thắng. QuotesControllerTests; CrmBusinessPipelineTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="61" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>27</v>
       </c>
@@ -11390,8 +11484,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
+      <c r="C4" s="110" t="inlineStr">
+        <is>
+          <t>Có BOQ catalog/revision, nhập cấu hình, preview và validation (BoqConfiguredWorkbookService, ConfiguredBoqControllerTests). Yêu cầu lỗi gốc chưa có bước tái hiện cụ thể, chưa xác nhận UAT; giữ Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>29</v>
       </c>
@@ -11400,8 +11499,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
+      <c r="C5" s="110" t="inlineStr">
+        <is>
+          <t>CapabilityDocumentsController/CapabilityDocumentService và CapabilityDocuments.tsx có CRUD/phân quyền; CapabilityDocumentsControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>31</v>
       </c>
@@ -11410,8 +11514,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
+      <c r="C6" s="110" t="inlineStr">
+        <is>
+          <t>ContractService tự sinh số khi để trống, cho nhập số riêng/kiểm tra trùng; Contracts.tsx có preview gợi ý. ContractsControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>34</v>
       </c>
@@ -11420,8 +11529,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
+      <c r="C7" s="110" t="inlineStr">
+        <is>
+          <t>ContractDetail có hướng dẫn VO qua i18n; ContractAppendixService xử lý phát sinh/duyệt. Không đổi trạng thái đã có.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
@@ -11430,8 +11544,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
+      <c r="C8" s="110" t="inlineStr">
+        <is>
+          <t>ContractDetail/ContractCareActivities hiển thị event qua i18n; seed bản dịch 4 ngôn ngữ. Giữ Implemented theo source; chưa chạy lại UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="19" t="s">
         <v>43</v>
       </c>
@@ -11440,8 +11559,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
+      <c r="C9" s="110" t="inlineStr">
+        <is>
+          <t>Design schedule task có assignee/approver/CC và dependency, cho việc không phụ thuộc chạy song song. DetailDesignScheduleService; DetailDesignScheduleControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="61" customHeight="1">
       <c r="A10" s="19" t="s">
         <v>46</v>
       </c>
@@ -11450,8 +11574,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
+      <c r="C10" s="110" t="inlineStr">
+        <is>
+          <t>Có mẫu BOQ NICON trong docs/Nicon/BOQ và nhập preview/mapping danh mục. Chưa có schema tổng quát giữ hierarchy/provenance/công thức cho mọi workbook; giữ Partial. BoqCatalogWorkbookService; Nicon-QLVH §7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>49</v>
       </c>
@@ -11460,8 +11589,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
+      <c r="C11" s="110" t="inlineStr">
+        <is>
+          <t>DesignProjectTeamTab và ProjectTeamService quản lý thành viên trên Operational Project; OperationalProjectTeamControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>51</v>
       </c>
@@ -11470,8 +11604,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
+      <c r="C12" s="110" t="inlineStr">
+        <is>
+          <t>Có deadline/checklist đấu thầu và lịch các giai đoạn thiết kế. TenderService; DetailDesignScheduleService; TendersControllerTests; DetailDesignScheduleControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="19" t="s">
         <v>56</v>
       </c>
@@ -11480,8 +11619,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
+      <c r="C13" s="110" t="inlineStr">
+        <is>
+          <t>DesignScheduleTab/Timeline có phase/task, kế hoạch/thực tế/trọng số. DetailDesignScheduleControllerTests. Nhập .mpp đầy đủ vẫn là Target riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="61" customHeight="1">
       <c r="A14" s="19" t="s">
         <v>60</v>
       </c>
@@ -11490,8 +11634,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
+      <c r="C14" s="110" t="inlineStr">
+        <is>
+          <t>Work package/design/tender có lịch và dependency. Chưa có SLA mọi công tác và quy tắc Lead 1 tuần được xác nhận/cấu hình; giữ Partial. DepartmentWorkPackageService; DetailDesignScheduleService.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="19" t="s">
         <v>63</v>
       </c>
@@ -11500,8 +11649,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
+      <c r="C15" s="110" t="inlineStr">
+        <is>
+          <t>Nhãn giao diện Detail Design qua i18n; tên entity/API ShopDrawing giữ tương thích. ShopDrawingTab; ShopDrawingsControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="19" t="s">
         <v>67</v>
       </c>
@@ -11510,8 +11664,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
+      <c r="C16" s="110" t="inlineStr">
+        <is>
+          <t>DesignProjectTeamTab/DesignScheduleTab có giao việc/duyệt; KpiService đọc tiến độ thiết kế. DetailDesignScheduleControllerTests; KpiControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="19" t="s">
         <v>69</v>
       </c>
@@ -11520,8 +11679,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
+      <c r="C17" s="110" t="inlineStr">
+        <is>
+          <t>ProjectDocumentService/ProjectDriveSyncService có durable sync nhiều module; chưa chứng minh tất cả đường upload/Drive NICON thật. Nicon-QLVH §9; ProjectDocumentServiceTests. Giữ Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="61" customHeight="1">
       <c r="A18" s="19" t="s">
         <v>74</v>
       </c>
@@ -11530,8 +11694,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
+      <c r="C18" s="110" t="inlineStr">
+        <is>
+          <t>OperationalProjectService/ProjectAccessService và báo cáo có scope dự án; aggregate thi công cũ còn DesignProjectId. Migration hợp nhất cần backfill/rehearsal/rollback; giữ Partial theo Nicon-QLVH §6.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="19" t="s">
         <v>77</v>
       </c>
@@ -11540,8 +11709,13 @@
           <t xml:space="preserve">Partial</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
+      <c r="C19" s="110" t="inlineStr">
+        <is>
+          <t>ProjectReportService có báo cáo dự án và XLSX/PDF, nguồn CM. actualCashflow/profitAndLoss/inventory chưa khả dụng trong báo cáo chung; ProjectReportsControllerTests. Giữ Partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="19" t="s">
         <v>82</v>
       </c>
@@ -11550,8 +11724,13 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
+      <c r="C20" s="110" t="inlineStr">
+        <is>
+          <t>Customer → nhiều OperationalProject; Opportunity có CustomerId/OperationalProjectId. OperationalProjectService; OpportunityService; OperationalProjectsControllerTests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
       <c r="A21" s="19" t="s">
         <v>86</v>
       </c>
@@ -11560,14 +11739,24 @@
           <t xml:space="preserve">Implemented</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
+      <c r="C21" s="110" t="inlineStr">
+        <is>
+          <t>DesignProject thuộc OperationalProject, bắt đầu trước HĐ đã ký. DesignProjectService; DesignProjectsControllerTests; Nicon-QLVH §4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>88</v>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Implemented</t>
+        </is>
+      </c>
+      <c r="C22" s="110" t="inlineStr">
+        <is>
+          <t>Có application_developer.md, user_guide.md, users-rbac.md và tài khoản seed. Đây là hướng dẫn trong repo, không xác nhận đã bàn giao host/tài khoản thật.</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11785,7 @@
     <col customWidth="1" min="8" max="8" width="18.43"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="44" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
@@ -11612,9 +11801,9 @@
       <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ghi chú — đối chiếu source d884b3c6, 20/10/2026</t>
+      <c r="F1" s="111" t="inlineStr">
+        <is>
+          <t>Ghi chú — đối chiếu source 7813bc5d, 21/10/2026; không chạy lại test, không xác nhận host/UAT</t>
         </is>
       </c>
       <c r="G1" s="12" t="s">
@@ -12058,7 +12247,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="95" customHeight="1">
       <c r="A21" s="17">
         <v>20.0</v>
       </c>
@@ -12070,9 +12259,9 @@
       <c r="E21" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Có tiến độ theo HĐ, nguồn Lead và timeline chăm sóc riêng; có lịch sử thì khóa đổi chiều.</t>
+      <c r="F21" s="114" t="inlineStr">
+        <is>
+          <t>Có nguồn Lead, tiến độ theo HĐ, phụ lục/mốc/file, chăm sóc riêng và email nhắc tự động. ContractExecutionProgressService; ContractReminderService; ContractSourceLeadsTests; ContractRemindersTests. Khóa đổi chiều từ lần bắt đầu gửi; Dự án vận hành là gốc nghiệp vụ.</t>
         </is>
       </c>
       <c r="G21" s="17"/>
@@ -12198,7 +12387,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="112" customHeight="1">
       <c r="A27" s="17">
         <v>26.0</v>
       </c>
@@ -12210,15 +12399,15 @@
       <c r="E27" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Có review nội bộ gắn file và ghi nhận quyết định khách; chưa có portal ký/markup trực tiếp.</t>
+      <c r="F27" s="113" t="inlineStr">
+        <is>
+          <t>Concept dossier: file theo loại/tầng, revision bất biến, feedback và kết quả xử lý, duyệt TK-M03 đã ký. ConceptDossierService/Panel; DesignReviewsControllerTests; ConceptFinalizationPersistenceTests; admin-concept-dossier.spec.ts. Portal/markup không thuộc gate hoàn thành đã xác nhận.</t>
         </is>
       </c>
       <c r="G27" s="17"/>
-      <c r="H27" s="25" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="H27" s="112" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13345,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="36" customHeight="1">
+    <row r="68" ht="78" customHeight="1">
       <c r="A68" s="17">
         <v>67.0</v>
       </c>
@@ -13168,9 +13357,9 @@
       <c r="E68" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="F68" s="103" t="inlineStr">
-        <is>
-          <t>Create/Edit form | Thiếu import đa sheet giữ hierarchy, provenance, công thức và tổng hợp đối soát.</t>
+      <c r="F68" s="113" t="inlineStr">
+        <is>
+          <t>Có BOQ draft/revision và nhập danh mục cấu hình. Còn thiếu import Execution BOQ đa sheet giữ hierarchy/provenance từng dòng, baseline và đối soát công thức. BoqCatalogWorkbookService; ProcurementService; Nicon-QLVH §7.</t>
         </is>
       </c>
       <c r="G68" s="17"/>
@@ -13574,7 +13763,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="78" customHeight="1">
       <c r="A86" s="17">
         <v>85.0</v>
       </c>
@@ -13588,8 +13777,10 @@
       <c r="E86" s="23" t="s">
         <v>488</v>
       </c>
-      <c r="F86" s="17" t="s">
-        <v>489</v>
+      <c r="F86" s="114" t="inlineStr">
+        <is>
+          <t>Target — FinanceService có Payment Request/period/correction; ProjectReportService khai báo actualCashflow unavailable. Chưa có sổ thực thu–chi/forecast tổng hợp. Không coi Paid milestone là ledger.</t>
+        </is>
       </c>
       <c r="G86" s="17"/>
       <c r="H86" s="25" t="inlineStr">
@@ -13598,7 +13789,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="61" customHeight="1">
       <c r="A87" s="17">
         <v>86.0</v>
       </c>
@@ -13612,8 +13803,10 @@
       <c r="E87" s="23" t="s">
         <v>493</v>
       </c>
-      <c r="F87" s="17" t="s">
-        <v>494</v>
+      <c r="F87" s="114" t="inlineStr">
+        <is>
+          <t>Target — ProjectReportService khai báo profitAndLoss/actualRevenue/actualExpenditure unavailable; chưa có nguồn ledger doanh thu/chi phí để tính P&amp;L.</t>
+        </is>
       </c>
       <c r="G87" s="17"/>
       <c r="H87" s="25" t="inlineStr">
@@ -13730,7 +13923,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="36" customHeight="1">
+    <row r="92" ht="78" customHeight="1">
       <c r="A92" s="17">
         <v>91.0</v>
       </c>
@@ -13744,9 +13937,9 @@
       <c r="E92" s="77" t="s">
         <v>289</v>
       </c>
-      <c r="F92" s="103" t="inlineStr">
-        <is>
-          <t>Setting + CRUD | Có cấu hình 6 nhóm KPI; thiếu framework đủ 11 vị trí NICON.</t>
+      <c r="F92" s="113" t="inlineStr">
+        <is>
+          <t>KpiService/KpiConfiguration: 19 metric, 6 nhóm scorecard; có trọng số/target/ngưỡng. Còn thiếu framework đủ 11 vị trí và nguồn HR/Admin. KpiControllerTests; Nicon-QLVH §10.</t>
         </is>
       </c>
       <c r="G92" s="78" t="s">
@@ -13758,7 +13951,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
+    <row r="93" ht="61" customHeight="1">
       <c r="A93" s="17">
         <v>92.0</v>
       </c>
@@ -13770,9 +13963,9 @@
       <c r="E93" s="77" t="s">
         <v>298</v>
       </c>
-      <c r="F93" s="103" t="inlineStr">
-        <is>
-          <t>Integration/rule config | Có mapping nguồn cho 19 chỉ số; thiếu nguồn/rule cho các vị trí còn lại.</t>
+      <c r="F93" s="113" t="inlineStr">
+        <is>
+          <t>KpiService có mapping 19 metric và MissingData; chưa đủ nguồn budget/S-Curve/tuyển dụng cho 11 vị trí. Nicon-QLVH §10; application_developer §7.19.</t>
         </is>
       </c>
       <c r="G93" s="79">
@@ -13784,7 +13977,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="36" customHeight="1">
+    <row r="94" ht="78" customHeight="1">
       <c r="A94" s="17">
         <v>93.0</v>
       </c>
@@ -13796,9 +13989,9 @@
       <c r="E94" s="77" t="s">
         <v>306</v>
       </c>
-      <c r="F94" s="103" t="inlineStr">
-        <is>
-          <t>Backend service | Có engine và khóa kỳ; thiếu chỉ số đầy đủ cho 11 vị trí.</t>
+      <c r="F94" s="113" t="inlineStr">
+        <is>
+          <t>Có tính ngày 01:00 giờ Việt Nam, tính thủ công, lịch sử và khóa snapshot; vẫn Partial theo phạm vi 11 vị trí. KpiCalculationBackgroundService; KpiService; KpiControllerTests.</t>
         </is>
       </c>
       <c r="G94" s="78" t="s">
@@ -13836,7 +14029,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
+    <row r="96" ht="61" customHeight="1">
       <c r="A96" s="17">
         <v>95.0</v>
       </c>
@@ -13848,9 +14041,9 @@
       <c r="E96" s="77" t="s">
         <v>322</v>
       </c>
-      <c r="F96" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Có CSV KPI theo nhân viên/kỳ; chưa có Google Sheets/PDF và lưu tự động lên Drive.</t>
+      <c r="F96" s="113" t="inlineStr">
+        <is>
+          <t>KpiController.Export hiện trả CSV theo nhân viên/kỳ. Chưa có Google Sheets/PDF, export toàn công ty và tự lưu Drive theo yêu cầu. Giữ Partial.</t>
         </is>
       </c>
       <c r="G96" s="79">
@@ -13998,7 +14191,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="61" customHeight="1">
       <c r="A102" s="17">
         <v>101.0</v>
       </c>
@@ -14014,8 +14207,10 @@
       <c r="E102" s="23" t="s">
         <v>543</v>
       </c>
-      <c r="F102" s="88" t="s">
-        <v>4</v>
+      <c r="F102" s="115" t="inlineStr">
+        <is>
+          <t>Chưa thấy global search/saved filters dùng chung; các module có tìm kiếm/lọc riêng. Giữ Target cho đúng phạm vi yêu cầu.</t>
+        </is>
       </c>
       <c r="G102" s="17"/>
       <c r="H102" s="25" t="inlineStr">

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4518,19 +4518,19 @@
       </c>
       <c r="E62" s="49"/>
     </row>
-    <row r="63" ht="44" customHeight="1">
+    <row r="63" ht="95" customHeight="1">
       <c r="A63" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="B63" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Target</t>
+      <c r="B63" s="106" t="inlineStr">
+        <is>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C63" s="37"/>
       <c r="D63" s="105" t="inlineStr">
         <is>
-          <t>Chưa thấy workflow tái ký/liên kết HĐ kế tiếp trong ContractService/ContractDetail. Email Renewal chỉ nhắc khách, không tạo/gia hạn HĐ mới.</t>
+          <t>Upstream đã ký → Renewal/Expansion → HĐ Draft độc lập hoặc Cơ hội đàm phán/Won/Lost. Nguồn/mục đích/lý do bất biến; cùng khách, chọn Dự án theo quyền; hỗ trợ tạo trực tiếp/Báo giá duyệt, truy vết hai chiều, idempotency và chặn xóa lịch sử. ContractContinuationRules; ContractContinuationsTests; contract-continuations.spec.ts (390/768px). Quy tắc theo chỉ đạo người dùng 22/10/2026; không tự đổi HĐ cũ. Không xác nhận production/UAT.</t>
         </is>
       </c>
       <c r="E63" s="49"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E62" s="49"/>
     </row>
-    <row r="63" ht="95" customHeight="1">
+    <row r="63" ht="112" customHeight="1">
       <c r="A63" s="44" t="s">
         <v>290</v>
       </c>
@@ -4530,7 +4530,7 @@
       <c r="C63" s="37"/>
       <c r="D63" s="105" t="inlineStr">
         <is>
-          <t>Upstream đã ký → Renewal/Expansion → HĐ Draft độc lập hoặc Cơ hội đàm phán/Won/Lost. Nguồn/mục đích/lý do bất biến; cùng khách, chọn Dự án theo quyền; hỗ trợ tạo trực tiếp/Báo giá duyệt, truy vết hai chiều, idempotency và chặn xóa lịch sử. ContractContinuationRules; ContractContinuationsTests; contract-continuations.spec.ts (390/768px). Quy tắc theo chỉ đạo người dùng 22/10/2026; không tự đổi HĐ cũ. Không xác nhận production/UAT.</t>
+          <t>Upstream đã ký → Renewal/Expansion → HĐ Draft riêng hoặc Cơ hội đàm phán/Won/Lost; truy vết nguồn bất biến, phân quyền, idempotency, chặn xóa lịch sử. Review UI/UX: hủy form rồi tạo độc lập; lỗi tải nguồn/thử lại; cập nhật nguồn khi xung đột mà giữ nội dung; lý do nhiều dòng, focus lỗi. Regression: 154 unit, 120 integration; E2E 390/768/1440px, bàn phím, vi/en/zh/ja. Không tự đổi HĐ cũ. Theo chỉ đạo người dùng 22/10/2026. Không xác nhận production/UAT; không hỗ trợ mở trang chưa tải khi hoàn toàn offline.</t>
         </is>
       </c>
       <c r="E63" s="49"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -2866,7 +2866,7 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="121">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3174,6 +3174,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5154,7 +5169,7 @@
       <c r="D110" s="44"/>
       <c r="E110" s="39"/>
     </row>
-    <row r="111">
+    <row r="111" ht="70" customHeight="1">
       <c r="A111" s="40" t="s">
         <v>515</v>
       </c>
@@ -5164,7 +5179,11 @@
         </is>
       </c>
       <c r="C111" s="37"/>
-      <c r="D111" s="48"/>
+      <c r="D111" s="116" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Implemented phần setup PM/Admin. Chặn thêm permit/task vào gói Completed/Cancelled. Hợp đồng khác chỉ dùng lại gói Completed có snapshot khi không sửa hồ sơ. Regression integration đã pass.</t>
+        </is>
+      </c>
       <c r="E111" s="49"/>
     </row>
     <row r="112">
@@ -5180,7 +5199,7 @@
       <c r="D112" s="48"/>
       <c r="E112" s="49"/>
     </row>
-    <row r="113">
+    <row r="113" ht="95" customHeight="1">
       <c r="A113" s="40" t="s">
         <v>518</v>
       </c>
@@ -5190,9 +5209,9 @@
         </is>
       </c>
       <c r="C113" s="37"/>
-      <c r="D113" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Có checklist theo Dự án; CM/NICON chưa duyệt template bắt buộc theo loại/quy mô công trình.</t>
+      <c r="D113" s="117" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Implemented phần mềm soạn mẫu 4 ngôn ngữ, duyệt độc lập, phiên bản/retire, snapshot dự án và kiểm tra mục bắt buộc. Toàn phạm vi vẫn Partial. Open decision Q-09 — CM/NICON chốt ma trận theo loại/quy mô, miễn/ngoại lệ và permit chặn từng mốc khởi công. PM hiện chọn mẫu thủ công. GĐ/ĐDCL/TKISO xác nhận ủy quyền phát hành điện tử, thu hồi, lưu/hủy hồ sơ ISO.</t>
         </is>
       </c>
       <c r="E113" s="81"/>
@@ -5236,7 +5255,7 @@
       <c r="D116" s="84"/>
       <c r="E116" s="83"/>
     </row>
-    <row r="117">
+    <row r="117" ht="70" customHeight="1">
       <c r="A117" s="40" t="s">
         <v>524</v>
       </c>
@@ -5246,7 +5265,11 @@
         </is>
       </c>
       <c r="C117" s="37"/>
-      <c r="D117" s="84"/>
+      <c r="D117" s="118" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Implemented phân công thành viên dự án, người duyệt độc lập, lịch và predecessor. Permit đã có task cùng dự án làm predecessor cho việc mới. Token cũ bị từ chối 409. Đổi lịch/chủ trì lưu history trước/sau và actor. Regression integration và live E2E đã pass.</t>
+        </is>
+      </c>
       <c r="E117" s="83"/>
     </row>
     <row r="118">
@@ -12691,7 +12714,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="70" customHeight="1">
       <c r="A40" s="17">
         <v>39.0</v>
       </c>
@@ -12707,8 +12730,10 @@
       <c r="E40" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="F40" s="17" t="s">
-        <v>26</v>
+      <c r="F40" s="119" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Implemented danh sách permit theo dự án và quản lý mẫu. Có mẫu 4 ngôn ngữ, duyệt độc lập, phiên bản/retire. Demo chỉ có mẫu nháp. CM/NICON cần duyệt nội dung mẫu sản xuất theo Q-09.</t>
+        </is>
       </c>
       <c r="G40" s="17"/>
       <c r="H40" s="25" t="inlineStr">
@@ -12717,7 +12742,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="80" customHeight="1">
       <c r="A41" s="17">
         <v>40.0</v>
       </c>
@@ -12729,8 +12754,10 @@
       <c r="E41" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="F41" s="17" t="s">
-        <v>33</v>
+      <c r="F41" s="119" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Implemented setup bằng mẫu Published, snapshot và mục bắt buộc. Chặn sửa gói đóng, stale request trả 409, lưu history lịch/chủ trì. GPXD hiện hữu làm predecessor cho PCCC mới. Checklist tự khớp loại/quy mô còn Partial: CM/NICON chốt Q-09, ngoại lệ và gate khởi công.</t>
+        </is>
       </c>
       <c r="G41" s="17"/>
       <c r="H41" s="25" t="inlineStr">
@@ -12739,7 +12766,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="70" customHeight="1">
       <c r="A42" s="17">
         <v>41.0</v>
       </c>
@@ -12751,8 +12778,10 @@
       <c r="E42" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="F42" s="17" t="s">
-        <v>38</v>
+      <c r="F42" s="119" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Giữ Implemented hồ sơ/trạng thái/timeline. Đã xác nhận phạm vi Legal bằng 21 unit, 25 integration, 2 live E2E trên Compose và 2 UI mock riêng. Live E2E gồm mobile/tablet và phục hồi stale edit. Không xác nhận host/UAT NICON.</t>
+        </is>
       </c>
       <c r="G42" s="17"/>
       <c r="H42" s="25" t="inlineStr">
@@ -14247,7 +14276,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="36" customHeight="1">
+    <row r="104" ht="70" customHeight="1">
       <c r="A104" s="17">
         <v>103.0</v>
       </c>
@@ -14263,9 +14292,9 @@
       <c r="E104" s="23" t="s">
         <v>552</v>
       </c>
-      <c r="F104" s="103" t="inlineStr">
-        <is>
-          <t>Chức năng chung | Có master data dùng chung; thiếu template/checklist theo dự án và approval matrix NICON.</t>
+      <c r="F104" s="120" t="inlineStr">
+        <is>
+          <t>22/10/2026, 75f41b6d: Có master data và engine mẫu checklist Pháp lý 4 ngôn ngữ, duyệt độc lập, phiên bản, snapshot dự án. Giữ Partial: CM/NICON chốt ma trận theo loại/quy mô, miễn/ngoại lệ, gate áp dụng và approval matrix chính thức. GĐ/ĐDCL/TKISO xác nhận ủy quyền phát hành/lưu hủy ISO.</t>
         </is>
       </c>
       <c r="G104" s="17"/>

--- a/docs/Nicon_BreakTask_v1.xlsx
+++ b/docs/Nicon_BreakTask_v1.xlsx
@@ -4870,13 +4870,13 @@
       </c>
       <c r="B89" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C89" s="37"/>
       <c r="D89" s="44" t="inlineStr">
         <is>
-          <t>Có hồ sơ Shop Drawing theo bộ môn; thiếu liên kết bản vẽ đến WBS/hạng mục thi công ổn định.</t>
+          <t>22/10/2026, 491f0038. IFC–WBS có API/UI, test đạt. PR #301 mở; chưa xác nhận host/UAT.</t>
         </is>
       </c>
       <c r="E89" s="39"/>
